--- a/Prusa Work/Adhesion Testing/Optimization Testing/Optimal Design Runs.xlsx
+++ b/Prusa Work/Adhesion Testing/Optimization Testing/Optimal Design Runs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github Stuff\Cylindrical-4th-Axis-Printer\Prusa Work\Adhesion Testing\Optimization Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509537DA-C726-4059-BDFF-D442AEB42B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FA73F4-6FB5-4748-AEB4-D1421FBE265E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6" yWindow="6" windowWidth="23028" windowHeight="12228" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Run</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>From Variance Testing</t>
+  </si>
+  <si>
+    <t>Shaft collar failed on ADMET, sample must be repeated</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -142,13 +148,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}" name="Table4" displayName="Table4" ref="B2:K104" totalsRowShown="0">
-  <autoFilter ref="B2:K104" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="5"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B2:K104" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9C86E860-61AA-4FEE-8EB4-A30E954E2ABD}" name="Run" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{A20EC31A-F218-4399-BC4B-A51A407258CC}" name="Mandrel"/>
@@ -475,7 +475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B3">
         <v>1</v>
       </c>
@@ -504,7 +504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B4">
         <v>1</v>
       </c>
@@ -530,7 +530,7 @@
         <v>73.643699999999995</v>
       </c>
     </row>
-    <row r="5" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B5">
         <v>1</v>
       </c>
@@ -556,7 +556,7 @@
         <v>89.305999999999997</v>
       </c>
     </row>
-    <row r="6" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B6">
         <v>1</v>
       </c>
@@ -582,7 +582,7 @@
         <v>73.695700000000002</v>
       </c>
     </row>
-    <row r="7" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B7">
         <v>1</v>
       </c>
@@ -608,7 +608,7 @@
         <v>48.312100000000001</v>
       </c>
     </row>
-    <row r="8" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B8">
         <v>1</v>
       </c>
@@ -634,7 +634,7 @@
         <v>85.577500000000001</v>
       </c>
     </row>
-    <row r="9" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B9">
         <v>2</v>
       </c>
@@ -663,7 +663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B10">
         <v>2</v>
       </c>
@@ -689,7 +689,7 @@
         <v>100.43049999999999</v>
       </c>
     </row>
-    <row r="11" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B11">
         <v>2</v>
       </c>
@@ -715,7 +715,7 @@
         <v>90.388499999999993</v>
       </c>
     </row>
-    <row r="12" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B12">
         <v>2</v>
       </c>
@@ -741,7 +741,7 @@
         <v>101.8031</v>
       </c>
     </row>
-    <row r="13" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B13">
         <v>2</v>
       </c>
@@ -767,7 +767,7 @@
         <v>62.641399999999997</v>
       </c>
     </row>
-    <row r="14" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B14">
         <v>2</v>
       </c>
@@ -793,7 +793,7 @@
         <v>72.420699999999997</v>
       </c>
     </row>
-    <row r="15" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B15">
         <v>3</v>
       </c>
@@ -822,7 +822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B16">
         <v>3</v>
       </c>
@@ -848,7 +848,7 @@
         <v>85.453800000000001</v>
       </c>
     </row>
-    <row r="17" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B17">
         <v>3</v>
       </c>
@@ -874,7 +874,7 @@
         <v>82.852099999999993</v>
       </c>
     </row>
-    <row r="18" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B18">
         <v>3</v>
       </c>
@@ -900,7 +900,7 @@
         <v>103.39100000000001</v>
       </c>
     </row>
-    <row r="19" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B19">
         <v>3</v>
       </c>
@@ -926,7 +926,7 @@
         <v>59.873199999999997</v>
       </c>
     </row>
-    <row r="20" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B20">
         <v>3</v>
       </c>
@@ -952,7 +952,7 @@
         <v>63.8598</v>
       </c>
     </row>
-    <row r="21" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B21">
         <v>4</v>
       </c>
@@ -975,7 +975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B22">
         <v>4</v>
       </c>
@@ -998,7 +998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B23">
         <v>4</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="24" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B24">
         <v>4</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="25" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B25">
         <v>4</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B26">
         <v>4</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="33" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B33">
         <v>6</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="34" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B34">
         <v>6</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B35">
         <v>6</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="36" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B36">
         <v>6</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="37" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B37">
         <v>6</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B38">
         <v>6</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B39">
         <v>7</v>
       </c>
@@ -1388,8 +1388,11 @@
       <c r="H39">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B40">
         <v>7</v>
       </c>
@@ -1411,8 +1414,11 @@
       <c r="H40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B41">
         <v>7</v>
       </c>
@@ -1435,7 +1441,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="42" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B42">
         <v>7</v>
       </c>
@@ -1458,7 +1464,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="43" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B43">
         <v>7</v>
       </c>
@@ -1481,7 +1487,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="44" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B44">
         <v>7</v>
       </c>
@@ -1504,7 +1510,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="45" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B45">
         <v>8</v>
       </c>
@@ -1527,7 +1533,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="46" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B46">
         <v>8</v>
       </c>
@@ -1550,7 +1556,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="47" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B47">
         <v>8</v>
       </c>
@@ -1573,7 +1579,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="48" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B48">
         <v>8</v>
       </c>
@@ -1596,7 +1602,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="49" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B49">
         <v>8</v>
       </c>
@@ -1619,7 +1625,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="50" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B50">
         <v>8</v>
       </c>
@@ -1642,7 +1648,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="51" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B51">
         <v>9</v>
       </c>
@@ -1665,7 +1671,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="52" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B52">
         <v>9</v>
       </c>
@@ -1688,7 +1694,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="53" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B53">
         <v>9</v>
       </c>
@@ -1711,7 +1717,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="54" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B54">
         <v>9</v>
       </c>
@@ -1734,7 +1740,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="55" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B55">
         <v>9</v>
       </c>
@@ -1757,7 +1763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B56">
         <v>9</v>
       </c>
@@ -1780,7 +1786,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="57" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B57">
         <v>10</v>
       </c>
@@ -1803,7 +1809,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="58" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B58">
         <v>10</v>
       </c>
@@ -1826,7 +1832,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="59" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B59">
         <v>10</v>
       </c>
@@ -1849,7 +1855,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="60" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B60">
         <v>10</v>
       </c>
@@ -1872,7 +1878,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="61" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B61">
         <v>10</v>
       </c>
@@ -1895,7 +1901,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="62" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B62">
         <v>10</v>
       </c>
@@ -1918,7 +1924,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="63" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B63">
         <v>11</v>
       </c>
@@ -1941,7 +1947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B64">
         <v>11</v>
       </c>
@@ -1964,7 +1970,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="65" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B65">
         <v>11</v>
       </c>
@@ -1987,7 +1993,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="66" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B66">
         <v>11</v>
       </c>
@@ -2010,7 +2016,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="67" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B67">
         <v>11</v>
       </c>
@@ -2033,7 +2039,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="68" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B68">
         <v>11</v>
       </c>
@@ -2056,7 +2062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B69">
         <v>12</v>
       </c>
@@ -2079,7 +2085,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="70" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B70">
         <v>12</v>
       </c>
@@ -2102,7 +2108,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="71" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B71">
         <v>12</v>
       </c>
@@ -2125,7 +2131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B72">
         <v>12</v>
       </c>
@@ -2148,7 +2154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B73">
         <v>12</v>
       </c>
@@ -2171,7 +2177,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="74" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B74">
         <v>12</v>
       </c>
@@ -2194,7 +2200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B75">
         <v>13</v>
       </c>
@@ -2217,7 +2223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B76">
         <v>13</v>
       </c>
@@ -2240,7 +2246,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="77" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B77">
         <v>13</v>
       </c>
@@ -2263,7 +2269,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="78" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B78">
         <v>13</v>
       </c>
@@ -2286,7 +2292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B79">
         <v>13</v>
       </c>
@@ -2309,7 +2315,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="80" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B80">
         <v>13</v>
       </c>
@@ -2332,7 +2338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B81">
         <v>14</v>
       </c>
@@ -2355,7 +2361,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="82" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B82">
         <v>14</v>
       </c>
@@ -2378,7 +2384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B83">
         <v>14</v>
       </c>
@@ -2401,7 +2407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B84">
         <v>14</v>
       </c>
@@ -2424,7 +2430,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="85" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B85">
         <v>14</v>
       </c>
@@ -2447,7 +2453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B86">
         <v>14</v>
       </c>
@@ -2470,7 +2476,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="87" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B87">
         <v>15</v>
       </c>
@@ -2493,7 +2499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B88">
         <v>15</v>
       </c>
@@ -2516,7 +2522,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="89" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B89">
         <v>15</v>
       </c>
@@ -2539,7 +2545,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="90" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B90">
         <v>15</v>
       </c>
@@ -2562,7 +2568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B91">
         <v>15</v>
       </c>
@@ -2585,7 +2591,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="92" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B92">
         <v>15</v>
       </c>
@@ -2608,7 +2614,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="93" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="1">
         <v>16</v>
       </c>
@@ -2631,7 +2637,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="94" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="1">
         <v>16</v>
       </c>
@@ -2654,7 +2660,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="95" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="1">
         <v>16</v>
       </c>
@@ -2677,7 +2683,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="96" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="1">
         <v>16</v>
       </c>
@@ -2700,7 +2706,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="97" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="1">
         <v>16</v>
       </c>
@@ -2723,7 +2729,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="98" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="1">
         <v>16</v>
       </c>
@@ -2746,7 +2752,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="99" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="1">
         <v>17</v>
       </c>
@@ -2769,7 +2775,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="100" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="1">
         <v>17</v>
       </c>
@@ -2792,7 +2798,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="101" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="1">
         <v>17</v>
       </c>
@@ -2815,7 +2821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="1">
         <v>17</v>
       </c>
@@ -2838,7 +2844,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="103" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="1">
         <v>17</v>
       </c>
@@ -2861,7 +2867,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="104" spans="2:8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="1">
         <v>17</v>
       </c>

--- a/Prusa Work/Adhesion Testing/Optimization Testing/Optimal Design Runs.xlsx
+++ b/Prusa Work/Adhesion Testing/Optimization Testing/Optimal Design Runs.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github Stuff\Cylindrical-4th-Axis-Printer\Prusa Work\Adhesion Testing\Optimization Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FA73F4-6FB5-4748-AEB4-D1421FBE265E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC7F20C-57EC-4092-A71E-3D3C17F9A03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
     <t>Run</t>
   </si>
@@ -71,10 +72,13 @@
     <t>From Variance Testing</t>
   </si>
   <si>
-    <t>Shaft collar failed on ADMET, sample must be repeated</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Shaft collar failed on ADMET, sample must be repeated. Video was recorded at 119.9 fps</t>
+  </si>
+  <si>
+    <t>Started taking pictures of post-break mesh</t>
   </si>
 </sst>
 </file>
@@ -90,15 +94,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor theme="5" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -106,16 +116,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -974,6 +999,9 @@
       <c r="H21">
         <v>2</v>
       </c>
+      <c r="I21">
+        <v>58.163179999999997</v>
+      </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B22">
@@ -997,6 +1025,9 @@
       <c r="H22">
         <v>2</v>
       </c>
+      <c r="I22">
+        <v>73.379589999999993</v>
+      </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B23">
@@ -1020,6 +1051,9 @@
       <c r="H23">
         <v>1.75</v>
       </c>
+      <c r="I23">
+        <v>71.820710000000005</v>
+      </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B24">
@@ -1043,6 +1077,9 @@
       <c r="H24">
         <v>1.75</v>
       </c>
+      <c r="I24">
+        <v>45.514893000000001</v>
+      </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B25">
@@ -1066,6 +1103,9 @@
       <c r="H25">
         <v>2</v>
       </c>
+      <c r="I25">
+        <v>49.046460000000003</v>
+      </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B26">
@@ -1089,6 +1129,9 @@
       <c r="H26">
         <v>2</v>
       </c>
+      <c r="I26">
+        <v>90.490819999999999</v>
+      </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B27">
@@ -1112,6 +1155,9 @@
       <c r="H27">
         <v>1.75</v>
       </c>
+      <c r="I27">
+        <v>61.297767999999998</v>
+      </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B28">
@@ -1135,6 +1181,9 @@
       <c r="H28">
         <v>1.5</v>
       </c>
+      <c r="I28">
+        <v>27.887608</v>
+      </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B29">
@@ -1158,6 +1207,9 @@
       <c r="H29">
         <v>2</v>
       </c>
+      <c r="I29">
+        <v>82.294780000000003</v>
+      </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B30">
@@ -1181,6 +1233,9 @@
       <c r="H30">
         <v>2</v>
       </c>
+      <c r="I30">
+        <v>95.025509999999997</v>
+      </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B31">
@@ -1204,6 +1259,9 @@
       <c r="H31">
         <v>1.75</v>
       </c>
+      <c r="I31">
+        <v>66.340900000000005</v>
+      </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B32">
@@ -1227,6 +1285,9 @@
       <c r="H32">
         <v>1.75</v>
       </c>
+      <c r="I32">
+        <v>81.566479999999999</v>
+      </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B33">
@@ -1250,6 +1311,9 @@
       <c r="H33">
         <v>1.75</v>
       </c>
+      <c r="I33">
+        <v>65.366780000000006</v>
+      </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B34">
@@ -1273,6 +1337,9 @@
       <c r="H34">
         <v>2</v>
       </c>
+      <c r="I34">
+        <v>48.211280000000002</v>
+      </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B35">
@@ -1296,6 +1363,9 @@
       <c r="H35">
         <v>1.5</v>
       </c>
+      <c r="I35">
+        <v>63.125390000000003</v>
+      </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B36">
@@ -1319,6 +1389,9 @@
       <c r="H36">
         <v>1.75</v>
       </c>
+      <c r="I36">
+        <v>64.643060000000006</v>
+      </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B37">
@@ -1342,6 +1415,9 @@
       <c r="H37">
         <v>2</v>
       </c>
+      <c r="I37">
+        <v>57.120350000000002</v>
+      </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B38">
@@ -1365,6 +1441,9 @@
       <c r="H38">
         <v>2</v>
       </c>
+      <c r="I38">
+        <v>42.58032</v>
+      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B39">
@@ -1388,8 +1467,11 @@
       <c r="H39">
         <v>2</v>
       </c>
+      <c r="I39">
+        <v>81.826035000000005</v>
+      </c>
       <c r="J39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -1414,8 +1496,11 @@
       <c r="H40">
         <v>2</v>
       </c>
+      <c r="I40">
+        <v>45.766823000000002</v>
+      </c>
       <c r="J40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.55000000000000004">
@@ -1440,6 +1525,9 @@
       <c r="H41">
         <v>1.75</v>
       </c>
+      <c r="I41">
+        <v>42.836829999999999</v>
+      </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B42">
@@ -1463,6 +1551,9 @@
       <c r="H42">
         <v>1.75</v>
       </c>
+      <c r="I42">
+        <v>45.427864</v>
+      </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B43">
@@ -1486,6 +1577,9 @@
       <c r="H43">
         <v>1.75</v>
       </c>
+      <c r="I43">
+        <v>55.901940000000003</v>
+      </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B44">
@@ -1509,6 +1603,9 @@
       <c r="H44">
         <v>1.5</v>
       </c>
+      <c r="I44">
+        <v>45.398857</v>
+      </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B45">
@@ -1532,6 +1629,9 @@
       <c r="H45">
         <v>1.75</v>
       </c>
+      <c r="I45">
+        <v>55.978282999999998</v>
+      </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B46">
@@ -1555,6 +1655,9 @@
       <c r="H46">
         <v>1.5</v>
       </c>
+      <c r="I46">
+        <v>99.326599999999999</v>
+      </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B47">
@@ -1578,6 +1681,12 @@
       <c r="H47">
         <v>1.5</v>
       </c>
+      <c r="I47">
+        <v>98.494479999999996</v>
+      </c>
+      <c r="J47" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B48">
@@ -1601,8 +1710,11 @@
       <c r="H48">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I48">
+        <v>42.645977000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B49">
         <v>8</v>
       </c>
@@ -1624,8 +1736,11 @@
       <c r="H49">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I49">
+        <v>50.823695999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B50">
         <v>8</v>
       </c>
@@ -1647,8 +1762,11 @@
       <c r="H50">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I50">
+        <v>92.132164000000003</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B51">
         <v>9</v>
       </c>
@@ -1670,8 +1788,11 @@
       <c r="H51">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I51">
+        <v>51.168754999999997</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B52">
         <v>9</v>
       </c>
@@ -1693,8 +1814,11 @@
       <c r="H52">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I52">
+        <v>65.939350000000005</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B53">
         <v>9</v>
       </c>
@@ -1716,8 +1840,11 @@
       <c r="H53">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I53">
+        <v>64.252189999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B54">
         <v>9</v>
       </c>
@@ -1739,8 +1866,11 @@
       <c r="H54">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I54">
+        <v>76.228675999999993</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B55">
         <v>9</v>
       </c>
@@ -1762,8 +1892,11 @@
       <c r="H55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I55">
+        <v>42.958973</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B56">
         <v>9</v>
       </c>
@@ -1785,8 +1918,11 @@
       <c r="H56">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I56">
+        <v>66.652373999999995</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B57">
         <v>10</v>
       </c>
@@ -1808,8 +1944,11 @@
       <c r="H57">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I57">
+        <v>50.625205999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B58">
         <v>10</v>
       </c>
@@ -1831,8 +1970,11 @@
       <c r="H58">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I58">
+        <v>26.986775999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B59">
         <v>10</v>
       </c>
@@ -1854,8 +1996,11 @@
       <c r="H59">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I59">
+        <v>86.737859999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B60">
         <v>10</v>
       </c>
@@ -1877,8 +2022,11 @@
       <c r="H60">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I60">
+        <v>85.203400000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B61">
         <v>10</v>
       </c>
@@ -1900,8 +2048,11 @@
       <c r="H61">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I61">
+        <v>34.509483000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B62">
         <v>10</v>
       </c>
@@ -1923,8 +2074,11 @@
       <c r="H62">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I62">
+        <v>42.255108</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B63">
         <v>11</v>
       </c>
@@ -1946,8 +2100,11 @@
       <c r="H63">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I63">
+        <v>64.363650000000007</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B64">
         <v>11</v>
       </c>
@@ -1969,8 +2126,11 @@
       <c r="H64">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I64">
+        <v>73.243706000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B65">
         <v>11</v>
       </c>
@@ -1992,8 +2152,11 @@
       <c r="H65">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I65">
+        <v>44.737735999999998</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B66">
         <v>11</v>
       </c>
@@ -2015,8 +2178,11 @@
       <c r="H66">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I66">
+        <v>53.043709999999997</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B67">
         <v>11</v>
       </c>
@@ -2038,8 +2204,11 @@
       <c r="H67">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I67">
+        <v>49.573214999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B68">
         <v>11</v>
       </c>
@@ -2061,8 +2230,11 @@
       <c r="H68">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I68">
+        <v>41.270297999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B69">
         <v>12</v>
       </c>
@@ -2084,8 +2256,11 @@
       <c r="H69">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I69">
+        <v>56.098903999999997</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B70">
         <v>12</v>
       </c>
@@ -2107,8 +2282,11 @@
       <c r="H70">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I70">
+        <v>44.398777000000003</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B71">
         <v>12</v>
       </c>
@@ -2130,8 +2308,11 @@
       <c r="H71">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I71">
+        <v>43.522379999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B72">
         <v>12</v>
       </c>
@@ -2153,8 +2334,11 @@
       <c r="H72">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I72">
+        <v>56.187457999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B73">
         <v>12</v>
       </c>
@@ -2176,8 +2360,11 @@
       <c r="H73">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I73">
+        <v>49.915230000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B74">
         <v>12</v>
       </c>
@@ -2199,8 +2386,11 @@
       <c r="H74">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I74">
+        <v>49.525886999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B75">
         <v>13</v>
       </c>
@@ -2222,8 +2412,11 @@
       <c r="H75">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I75">
+        <v>106.62945000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B76">
         <v>13</v>
       </c>
@@ -2245,8 +2438,11 @@
       <c r="H76">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I76">
+        <v>88.038730000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B77">
         <v>13</v>
       </c>
@@ -2268,8 +2464,11 @@
       <c r="H77">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I77">
+        <v>55.057602000000003</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B78">
         <v>13</v>
       </c>
@@ -2291,8 +2490,11 @@
       <c r="H78">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I78">
+        <v>49.835830000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B79">
         <v>13</v>
       </c>
@@ -2314,8 +2516,11 @@
       <c r="H79">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I79">
+        <v>46.455419999999997</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B80">
         <v>13</v>
       </c>
@@ -2337,8 +2542,11 @@
       <c r="H80">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I80">
+        <v>52.750557000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B81">
         <v>14</v>
       </c>
@@ -2360,8 +2568,11 @@
       <c r="H81">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I81">
+        <v>48.605206000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B82">
         <v>14</v>
       </c>
@@ -2383,8 +2594,11 @@
       <c r="H82">
         <v>2</v>
       </c>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I82">
+        <v>109.57774999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B83">
         <v>14</v>
       </c>
@@ -2406,8 +2620,11 @@
       <c r="H83">
         <v>2</v>
       </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I83">
+        <v>101.58937</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B84">
         <v>14</v>
       </c>
@@ -2429,8 +2646,11 @@
       <c r="H84">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I84">
+        <v>55.442363999999998</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B85">
         <v>14</v>
       </c>
@@ -2452,8 +2672,11 @@
       <c r="H85">
         <v>2</v>
       </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I85">
+        <v>96.187430000000006</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B86">
         <v>14</v>
       </c>
@@ -2475,8 +2698,11 @@
       <c r="H86">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I86">
+        <v>35.883629999999997</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B87">
         <v>15</v>
       </c>
@@ -2498,8 +2724,11 @@
       <c r="H87">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I87">
+        <v>99.925124999999994</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B88">
         <v>15</v>
       </c>
@@ -2521,8 +2750,11 @@
       <c r="H88">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I88">
+        <v>43.9163</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B89">
         <v>15</v>
       </c>
@@ -2544,8 +2776,11 @@
       <c r="H89">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I89">
+        <v>48.215865999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B90">
         <v>15</v>
       </c>
@@ -2567,8 +2802,11 @@
       <c r="H90">
         <v>2</v>
       </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I90">
+        <v>124.18344999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B91">
         <v>15</v>
       </c>
@@ -2590,8 +2828,11 @@
       <c r="H91">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I91">
+        <v>49.113639999999997</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B92">
         <v>15</v>
       </c>
@@ -2613,8 +2854,11 @@
       <c r="H92">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I92">
+        <v>66.881399999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="1">
         <v>16</v>
       </c>
@@ -2636,8 +2880,11 @@
       <c r="H93" s="2">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I93">
+        <v>112.68944500000001</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="1">
         <v>16</v>
       </c>
@@ -2659,8 +2906,11 @@
       <c r="H94" s="2">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I94">
+        <v>38.494520000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="1">
         <v>16</v>
       </c>
@@ -2682,8 +2932,11 @@
       <c r="H95" s="2">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I95">
+        <v>36.946303999999998</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="1">
         <v>16</v>
       </c>
@@ -2705,8 +2958,11 @@
       <c r="H96" s="2">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I96">
+        <v>68.568550000000002</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="1">
         <v>16</v>
       </c>
@@ -2728,8 +2984,11 @@
       <c r="H97" s="2">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I97">
+        <v>54.046840000000003</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="1">
         <v>16</v>
       </c>
@@ -2751,8 +3010,11 @@
       <c r="H98" s="2">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I98">
+        <v>53.924689999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="1">
         <v>17</v>
       </c>
@@ -2774,8 +3036,11 @@
       <c r="H99" s="2">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I99">
+        <v>56.175243000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="1">
         <v>17</v>
       </c>
@@ -2797,8 +3062,11 @@
       <c r="H100" s="2">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I100">
+        <v>87.840230000000005</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="1">
         <v>17</v>
       </c>
@@ -2820,8 +3088,11 @@
       <c r="H101" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I101">
+        <v>47.786822999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="1">
         <v>17</v>
       </c>
@@ -2843,8 +3114,11 @@
       <c r="H102" s="2">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I102">
+        <v>98.228806000000006</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="1">
         <v>17</v>
       </c>
@@ -2866,8 +3140,11 @@
       <c r="H103" s="2">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I103">
+        <v>24.220154000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="1">
         <v>17</v>
       </c>
@@ -2888,6 +3165,9 @@
       </c>
       <c r="H104" s="2">
         <v>1.5</v>
+      </c>
+      <c r="I104">
+        <v>38.463979999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2897,4 +3177,2392 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C9E5B5-BFB6-44FF-96EE-8C12013B51A8}">
+  <dimension ref="D1:J103"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="4" max="4" width="15.20703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.9453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.3125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.47265625" customWidth="1"/>
+    <col min="8" max="8" width="6.62890625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.68359375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.47265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D2" s="4">
+        <v>260</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H2" s="4">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4">
+        <v>95.796599999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D3" s="3">
+        <v>260</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3">
+        <v>73.643699999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D4" s="4">
+        <v>260</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
+        <v>3</v>
+      </c>
+      <c r="J4" s="4">
+        <v>89.305999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D5" s="3">
+        <v>260</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <v>4</v>
+      </c>
+      <c r="J5" s="3">
+        <v>73.695700000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D6" s="4">
+        <v>260</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
+        <v>5</v>
+      </c>
+      <c r="J6" s="4">
+        <v>48.312100000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D7" s="3">
+        <v>260</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>6</v>
+      </c>
+      <c r="J7" s="3">
+        <v>85.577500000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D8" s="4">
+        <v>260</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>54.3339</v>
+      </c>
+    </row>
+    <row r="9" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D9" s="3">
+        <v>260</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100.43049999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D10" s="4">
+        <v>260</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4">
+        <v>3</v>
+      </c>
+      <c r="J10" s="4">
+        <v>90.388499999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D11" s="3">
+        <v>260</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>4</v>
+      </c>
+      <c r="J11" s="3">
+        <v>101.8031</v>
+      </c>
+    </row>
+    <row r="12" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D12" s="4">
+        <v>260</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4">
+        <v>5</v>
+      </c>
+      <c r="J12" s="4">
+        <v>62.641399999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D13" s="3">
+        <v>260</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>6</v>
+      </c>
+      <c r="J13" s="3">
+        <v>72.420699999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D14" s="4">
+        <v>260</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4">
+        <v>63.475000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D15" s="3">
+        <v>260</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>85.453800000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D16" s="4">
+        <v>260</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4">
+        <v>3</v>
+      </c>
+      <c r="J16" s="4">
+        <v>82.852099999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D17" s="3">
+        <v>260</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3">
+        <v>103.39100000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D18" s="4">
+        <v>260</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H18" s="4">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4">
+        <v>5</v>
+      </c>
+      <c r="J18" s="4">
+        <v>59.873199999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D19" s="3">
+        <v>260</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3">
+        <v>6</v>
+      </c>
+      <c r="J19" s="3">
+        <v>63.8598</v>
+      </c>
+    </row>
+    <row r="20" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D20" s="4">
+        <v>240</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2</v>
+      </c>
+      <c r="H20" s="4">
+        <v>2</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4">
+        <v>58.163179999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D21" s="3">
+        <v>240</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2</v>
+      </c>
+      <c r="J21" s="3">
+        <v>73.379589999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D22" s="4">
+        <v>240</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H22" s="4">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4">
+        <v>3</v>
+      </c>
+      <c r="J22" s="4">
+        <v>71.820710000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D23" s="3">
+        <v>280</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3">
+        <v>45.514893000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D24" s="4">
+        <v>240</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>2</v>
+      </c>
+      <c r="H24" s="4">
+        <v>1</v>
+      </c>
+      <c r="I24" s="4">
+        <v>5</v>
+      </c>
+      <c r="J24" s="4">
+        <v>49.046460000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D25" s="3">
+        <v>240</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G25" s="3">
+        <v>2</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
+        <v>6</v>
+      </c>
+      <c r="J25" s="3">
+        <v>90.490819999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D26" s="4">
+        <v>280</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H26" s="4">
+        <v>1</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4">
+        <v>61.297767999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D27" s="3">
+        <v>280</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>2</v>
+      </c>
+      <c r="J27" s="3">
+        <v>27.887608</v>
+      </c>
+    </row>
+    <row r="28" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D28" s="4">
+        <v>240</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4">
+        <v>3</v>
+      </c>
+      <c r="J28" s="4">
+        <v>82.294780000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D29" s="3">
+        <v>240</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G29" s="3">
+        <v>2</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3">
+        <v>4</v>
+      </c>
+      <c r="J29" s="3">
+        <v>95.025509999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D30" s="4">
+        <v>240</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F30" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H30" s="4">
+        <v>1</v>
+      </c>
+      <c r="I30" s="4">
+        <v>5</v>
+      </c>
+      <c r="J30" s="4">
+        <v>66.340900000000005</v>
+      </c>
+    </row>
+    <row r="31" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D31" s="3">
+        <v>240</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
+        <v>6</v>
+      </c>
+      <c r="J31" s="3">
+        <v>81.566479999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D32" s="4">
+        <v>280</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H32" s="4">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4">
+        <v>65.366780000000006</v>
+      </c>
+    </row>
+    <row r="33" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D33" s="3">
+        <v>280</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G33" s="3">
+        <v>2</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2</v>
+      </c>
+      <c r="J33" s="3">
+        <v>48.211280000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D34" s="4">
+        <v>240</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F34" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G34" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H34" s="4">
+        <v>2</v>
+      </c>
+      <c r="I34" s="4">
+        <v>3</v>
+      </c>
+      <c r="J34" s="4">
+        <v>63.125390000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D35" s="3">
+        <v>240</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3">
+        <v>64.643060000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D36" s="4">
+        <v>280</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2</v>
+      </c>
+      <c r="H36" s="4">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4">
+        <v>5</v>
+      </c>
+      <c r="J36" s="4">
+        <v>57.120350000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D37" s="3">
+        <v>280</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G37" s="3">
+        <v>2</v>
+      </c>
+      <c r="H37" s="3">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <v>6</v>
+      </c>
+      <c r="J37" s="3">
+        <v>42.58032</v>
+      </c>
+    </row>
+    <row r="38" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D38" s="4">
+        <v>240</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G38" s="4">
+        <v>2</v>
+      </c>
+      <c r="H38" s="4">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4">
+        <v>1</v>
+      </c>
+      <c r="J38" s="4">
+        <v>81.826035000000005</v>
+      </c>
+    </row>
+    <row r="39" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D39" s="3">
+        <v>280</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G39" s="3">
+        <v>2</v>
+      </c>
+      <c r="H39" s="3">
+        <v>1</v>
+      </c>
+      <c r="I39" s="3">
+        <v>2</v>
+      </c>
+      <c r="J39" s="3">
+        <v>45.766823000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D40" s="4">
+        <v>280</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G40" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H40" s="4">
+        <v>1</v>
+      </c>
+      <c r="I40" s="4">
+        <v>3</v>
+      </c>
+      <c r="J40" s="4">
+        <v>42.836829999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D41" s="3">
+        <v>280</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2</v>
+      </c>
+      <c r="I41" s="3">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
+        <v>45.427864</v>
+      </c>
+    </row>
+    <row r="42" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D42" s="4">
+        <v>280</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G42" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H42" s="4">
+        <v>1</v>
+      </c>
+      <c r="I42" s="4">
+        <v>5</v>
+      </c>
+      <c r="J42" s="4">
+        <v>55.901940000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D43" s="3">
+        <v>280</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1</v>
+      </c>
+      <c r="I43" s="3">
+        <v>6</v>
+      </c>
+      <c r="J43" s="3">
+        <v>45.398857</v>
+      </c>
+    </row>
+    <row r="44" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D44" s="4">
+        <v>280</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G44" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H44" s="4">
+        <v>1</v>
+      </c>
+      <c r="I44" s="4">
+        <v>1</v>
+      </c>
+      <c r="J44" s="4">
+        <v>55.978282999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D45" s="3">
+        <v>240</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2</v>
+      </c>
+      <c r="J45" s="3">
+        <v>99.326599999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D46" s="4">
+        <v>240</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G46" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4">
+        <v>3</v>
+      </c>
+      <c r="J46" s="4">
+        <v>98.494479999999996</v>
+      </c>
+    </row>
+    <row r="47" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D47" s="3">
+        <v>280</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H47" s="3">
+        <v>2</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
+        <v>42.645977000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D48" s="4">
+        <v>240</v>
+      </c>
+      <c r="E48" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F48" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G48" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H48" s="4">
+        <v>2</v>
+      </c>
+      <c r="I48" s="4">
+        <v>5</v>
+      </c>
+      <c r="J48" s="4">
+        <v>50.823695999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D49" s="3">
+        <v>240</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2</v>
+      </c>
+      <c r="I49" s="3">
+        <v>6</v>
+      </c>
+      <c r="J49" s="3">
+        <v>92.132164000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D50" s="4">
+        <v>280</v>
+      </c>
+      <c r="E50" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F50" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G50" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H50" s="4">
+        <v>1</v>
+      </c>
+      <c r="I50" s="4">
+        <v>1</v>
+      </c>
+      <c r="J50" s="4">
+        <v>51.168754999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D51" s="3">
+        <v>280</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G51" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H51" s="3">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
+        <v>2</v>
+      </c>
+      <c r="J51" s="3">
+        <v>65.939350000000005</v>
+      </c>
+    </row>
+    <row r="52" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D52" s="4">
+        <v>280</v>
+      </c>
+      <c r="E52" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F52" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G52" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H52" s="4">
+        <v>1</v>
+      </c>
+      <c r="I52" s="4">
+        <v>3</v>
+      </c>
+      <c r="J52" s="4">
+        <v>64.252189999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D53" s="3">
+        <v>240</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G53" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3">
+        <v>4</v>
+      </c>
+      <c r="J53" s="3">
+        <v>76.228675999999993</v>
+      </c>
+    </row>
+    <row r="54" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D54" s="4">
+        <v>280</v>
+      </c>
+      <c r="E54" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F54" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G54" s="4">
+        <v>2</v>
+      </c>
+      <c r="H54" s="4">
+        <v>2</v>
+      </c>
+      <c r="I54" s="4">
+        <v>5</v>
+      </c>
+      <c r="J54" s="4">
+        <v>42.958973</v>
+      </c>
+    </row>
+    <row r="55" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D55" s="3">
+        <v>240</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G55" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H55" s="3">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3">
+        <v>6</v>
+      </c>
+      <c r="J55" s="3">
+        <v>66.652373999999995</v>
+      </c>
+    </row>
+    <row r="56" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D56" s="4">
+        <v>280</v>
+      </c>
+      <c r="E56" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F56" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G56" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H56" s="4">
+        <v>2</v>
+      </c>
+      <c r="I56" s="4">
+        <v>1</v>
+      </c>
+      <c r="J56" s="4">
+        <v>50.625205999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D57" s="3">
+        <v>280</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2</v>
+      </c>
+      <c r="J57" s="3">
+        <v>26.986775999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D58" s="4">
+        <v>240</v>
+      </c>
+      <c r="E58" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F58" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G58" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H58" s="4">
+        <v>0</v>
+      </c>
+      <c r="I58" s="4">
+        <v>3</v>
+      </c>
+      <c r="J58" s="4">
+        <v>86.737859999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D59" s="3">
+        <v>240</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2</v>
+      </c>
+      <c r="I59" s="3">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
+        <v>85.203400000000002</v>
+      </c>
+    </row>
+    <row r="60" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D60" s="4">
+        <v>240</v>
+      </c>
+      <c r="E60" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F60" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G60" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H60" s="4">
+        <v>2</v>
+      </c>
+      <c r="I60" s="4">
+        <v>5</v>
+      </c>
+      <c r="J60" s="4">
+        <v>34.509483000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D61" s="3">
+        <v>240</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>6</v>
+      </c>
+      <c r="J61" s="3">
+        <v>42.255108</v>
+      </c>
+    </row>
+    <row r="62" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D62" s="4">
+        <v>280</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F62" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G62" s="4">
+        <v>2</v>
+      </c>
+      <c r="H62" s="4">
+        <v>2</v>
+      </c>
+      <c r="I62" s="4">
+        <v>1</v>
+      </c>
+      <c r="J62" s="4">
+        <v>64.363650000000007</v>
+      </c>
+    </row>
+    <row r="63" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D63" s="3">
+        <v>240</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G63" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H63" s="3">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
+        <v>2</v>
+      </c>
+      <c r="J63" s="3">
+        <v>73.243706000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D64" s="4">
+        <v>280</v>
+      </c>
+      <c r="E64" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F64" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G64" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H64" s="4">
+        <v>0</v>
+      </c>
+      <c r="I64" s="4">
+        <v>3</v>
+      </c>
+      <c r="J64" s="4">
+        <v>44.737735999999998</v>
+      </c>
+    </row>
+    <row r="65" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D65" s="3">
+        <v>280</v>
+      </c>
+      <c r="E65" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G65" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H65" s="3">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3">
+        <v>4</v>
+      </c>
+      <c r="J65" s="3">
+        <v>53.043709999999997</v>
+      </c>
+    </row>
+    <row r="66" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D66" s="4">
+        <v>280</v>
+      </c>
+      <c r="E66" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F66" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G66" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H66" s="4">
+        <v>0</v>
+      </c>
+      <c r="I66" s="4">
+        <v>5</v>
+      </c>
+      <c r="J66" s="4">
+        <v>49.573214999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D67" s="3">
+        <v>280</v>
+      </c>
+      <c r="E67" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G67" s="3">
+        <v>2</v>
+      </c>
+      <c r="H67" s="3">
+        <v>2</v>
+      </c>
+      <c r="I67" s="3">
+        <v>6</v>
+      </c>
+      <c r="J67" s="3">
+        <v>41.270297999999997</v>
+      </c>
+    </row>
+    <row r="68" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D68" s="4">
+        <v>240</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G68" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H68" s="4">
+        <v>1</v>
+      </c>
+      <c r="I68" s="4">
+        <v>1</v>
+      </c>
+      <c r="J68" s="4">
+        <v>56.098903999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D69" s="3">
+        <v>280</v>
+      </c>
+      <c r="E69" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G69" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H69" s="3">
+        <v>2</v>
+      </c>
+      <c r="I69" s="3">
+        <v>2</v>
+      </c>
+      <c r="J69" s="3">
+        <v>44.398777000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D70" s="4">
+        <v>280</v>
+      </c>
+      <c r="E70" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F70" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G70" s="4">
+        <v>2</v>
+      </c>
+      <c r="H70" s="4">
+        <v>0</v>
+      </c>
+      <c r="I70" s="4">
+        <v>3</v>
+      </c>
+      <c r="J70" s="4">
+        <v>43.522379999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D71" s="3">
+        <v>280</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G71" s="3">
+        <v>2</v>
+      </c>
+      <c r="H71" s="3">
+        <v>1</v>
+      </c>
+      <c r="I71" s="3">
+        <v>4</v>
+      </c>
+      <c r="J71" s="3">
+        <v>56.187457999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D72" s="4">
+        <v>240</v>
+      </c>
+      <c r="E72" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F72" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G72" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H72" s="4">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4">
+        <v>5</v>
+      </c>
+      <c r="J72" s="4">
+        <v>49.915230000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D73" s="3">
+        <v>280</v>
+      </c>
+      <c r="E73" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="3">
+        <v>2</v>
+      </c>
+      <c r="H73" s="3">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3">
+        <v>6</v>
+      </c>
+      <c r="J73" s="3">
+        <v>49.525886999999997</v>
+      </c>
+    </row>
+    <row r="74" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D74" s="4">
+        <v>240</v>
+      </c>
+      <c r="E74" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F74" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G74" s="4">
+        <v>2</v>
+      </c>
+      <c r="H74" s="4">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4">
+        <v>1</v>
+      </c>
+      <c r="J74" s="4">
+        <v>106.62945000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D75" s="3">
+        <v>240</v>
+      </c>
+      <c r="E75" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F75" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G75" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H75" s="3">
+        <v>0</v>
+      </c>
+      <c r="I75" s="3">
+        <v>2</v>
+      </c>
+      <c r="J75" s="3">
+        <v>88.038730000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D76" s="4">
+        <v>240</v>
+      </c>
+      <c r="E76" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F76" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G76" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H76" s="4">
+        <v>1</v>
+      </c>
+      <c r="I76" s="4">
+        <v>3</v>
+      </c>
+      <c r="J76" s="4">
+        <v>55.057602000000003</v>
+      </c>
+    </row>
+    <row r="77" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D77" s="3">
+        <v>280</v>
+      </c>
+      <c r="E77" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G77" s="3">
+        <v>2</v>
+      </c>
+      <c r="H77" s="3">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3">
+        <v>4</v>
+      </c>
+      <c r="J77" s="3">
+        <v>49.835830000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D78" s="4">
+        <v>280</v>
+      </c>
+      <c r="E78" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F78" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G78" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H78" s="4">
+        <v>1</v>
+      </c>
+      <c r="I78" s="4">
+        <v>5</v>
+      </c>
+      <c r="J78" s="4">
+        <v>46.455419999999997</v>
+      </c>
+    </row>
+    <row r="79" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D79" s="3">
+        <v>280</v>
+      </c>
+      <c r="E79" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F79" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G79" s="3">
+        <v>2</v>
+      </c>
+      <c r="H79" s="3">
+        <v>2</v>
+      </c>
+      <c r="I79" s="3">
+        <v>6</v>
+      </c>
+      <c r="J79" s="3">
+        <v>52.750557000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D80" s="4">
+        <v>280</v>
+      </c>
+      <c r="E80" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F80" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G80" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H80" s="4">
+        <v>0</v>
+      </c>
+      <c r="I80" s="4">
+        <v>1</v>
+      </c>
+      <c r="J80" s="4">
+        <v>48.605206000000003</v>
+      </c>
+    </row>
+    <row r="81" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D81" s="3">
+        <v>240</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G81" s="3">
+        <v>2</v>
+      </c>
+      <c r="H81" s="3">
+        <v>2</v>
+      </c>
+      <c r="I81" s="3">
+        <v>2</v>
+      </c>
+      <c r="J81" s="3">
+        <v>109.57774999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D82" s="4">
+        <v>240</v>
+      </c>
+      <c r="E82" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F82" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="G82" s="4">
+        <v>2</v>
+      </c>
+      <c r="H82" s="4">
+        <v>2</v>
+      </c>
+      <c r="I82" s="4">
+        <v>3</v>
+      </c>
+      <c r="J82" s="4">
+        <v>101.58937</v>
+      </c>
+    </row>
+    <row r="83" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D83" s="3">
+        <v>240</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H83" s="3">
+        <v>1</v>
+      </c>
+      <c r="I83" s="3">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
+        <v>55.442363999999998</v>
+      </c>
+    </row>
+    <row r="84" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D84" s="4">
+        <v>240</v>
+      </c>
+      <c r="E84" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F84" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G84" s="4">
+        <v>2</v>
+      </c>
+      <c r="H84" s="4">
+        <v>0</v>
+      </c>
+      <c r="I84" s="4">
+        <v>5</v>
+      </c>
+      <c r="J84" s="4">
+        <v>96.187430000000006</v>
+      </c>
+    </row>
+    <row r="85" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D85" s="3">
+        <v>280</v>
+      </c>
+      <c r="E85" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F85" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G85" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H85" s="3">
+        <v>2</v>
+      </c>
+      <c r="I85" s="3">
+        <v>6</v>
+      </c>
+      <c r="J85" s="3">
+        <v>35.883629999999997</v>
+      </c>
+    </row>
+    <row r="86" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D86" s="4">
+        <v>240</v>
+      </c>
+      <c r="E86" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F86" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G86" s="4">
+        <v>2</v>
+      </c>
+      <c r="H86" s="4">
+        <v>2</v>
+      </c>
+      <c r="I86" s="4">
+        <v>1</v>
+      </c>
+      <c r="J86" s="4">
+        <v>99.925124999999994</v>
+      </c>
+    </row>
+    <row r="87" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D87" s="3">
+        <v>280</v>
+      </c>
+      <c r="E87" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F87" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G87" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H87" s="3">
+        <v>2</v>
+      </c>
+      <c r="I87" s="3">
+        <v>2</v>
+      </c>
+      <c r="J87" s="3">
+        <v>43.9163</v>
+      </c>
+    </row>
+    <row r="88" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D88" s="4">
+        <v>280</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F88" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G88" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="H88" s="4">
+        <v>1</v>
+      </c>
+      <c r="I88" s="4">
+        <v>3</v>
+      </c>
+      <c r="J88" s="4">
+        <v>48.215865999999998</v>
+      </c>
+    </row>
+    <row r="89" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D89" s="3">
+        <v>240</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G89" s="3">
+        <v>2</v>
+      </c>
+      <c r="H89" s="3">
+        <v>2</v>
+      </c>
+      <c r="I89" s="3">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
+        <v>124.18344999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D90" s="4">
+        <v>280</v>
+      </c>
+      <c r="E90" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="F90" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G90" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H90" s="4">
+        <v>1</v>
+      </c>
+      <c r="I90" s="4">
+        <v>5</v>
+      </c>
+      <c r="J90" s="4">
+        <v>49.113639999999997</v>
+      </c>
+    </row>
+    <row r="91" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D91" s="3">
+        <v>240</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G91" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="H91" s="3">
+        <v>1</v>
+      </c>
+      <c r="I91" s="3">
+        <v>6</v>
+      </c>
+      <c r="J91" s="3">
+        <v>66.881399999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D92" s="4">
+        <v>240</v>
+      </c>
+      <c r="E92" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="F92" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G92" s="5">
+        <v>1.75</v>
+      </c>
+      <c r="H92" s="4">
+        <v>1</v>
+      </c>
+      <c r="I92" s="4">
+        <v>1</v>
+      </c>
+      <c r="J92" s="4">
+        <v>112.68944500000001</v>
+      </c>
+    </row>
+    <row r="93" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D93" s="3">
+        <v>280</v>
+      </c>
+      <c r="E93" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F93" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="G93" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H93" s="3">
+        <v>2</v>
+      </c>
+      <c r="I93" s="3">
+        <v>2</v>
+      </c>
+      <c r="J93" s="3">
+        <v>38.494520000000001</v>
+      </c>
+    </row>
+    <row r="94" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D94" s="4">
+        <v>280</v>
+      </c>
+      <c r="E94" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F94" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G94" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="H94" s="4">
+        <v>2</v>
+      </c>
+      <c r="I94" s="4">
+        <v>3</v>
+      </c>
+      <c r="J94" s="4">
+        <v>36.946303999999998</v>
+      </c>
+    </row>
+    <row r="95" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D95" s="3">
+        <v>240</v>
+      </c>
+      <c r="E95" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="F95" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="G95" s="6">
+        <v>1.75</v>
+      </c>
+      <c r="H95" s="3">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3">
+        <v>4</v>
+      </c>
+      <c r="J95" s="3">
+        <v>68.568550000000002</v>
+      </c>
+    </row>
+    <row r="96" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D96" s="4">
+        <v>280</v>
+      </c>
+      <c r="E96" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="F96" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G96" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="H96" s="4">
+        <v>1</v>
+      </c>
+      <c r="I96" s="4">
+        <v>5</v>
+      </c>
+      <c r="J96" s="4">
+        <v>54.046840000000003</v>
+      </c>
+    </row>
+    <row r="97" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D97" s="3">
+        <v>280</v>
+      </c>
+      <c r="E97" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="F97" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="G97" s="6">
+        <v>1.75</v>
+      </c>
+      <c r="H97" s="3">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3">
+        <v>6</v>
+      </c>
+      <c r="J97" s="3">
+        <v>53.924689999999998</v>
+      </c>
+    </row>
+    <row r="98" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D98" s="4">
+        <v>240</v>
+      </c>
+      <c r="E98" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="F98" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G98" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="H98" s="4">
+        <v>2</v>
+      </c>
+      <c r="I98" s="4">
+        <v>1</v>
+      </c>
+      <c r="J98" s="4">
+        <v>56.175243000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D99" s="3">
+        <v>240</v>
+      </c>
+      <c r="E99" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="F99" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="G99" s="6">
+        <v>1.75</v>
+      </c>
+      <c r="H99" s="3">
+        <v>1</v>
+      </c>
+      <c r="I99" s="3">
+        <v>2</v>
+      </c>
+      <c r="J99" s="3">
+        <v>87.840230000000005</v>
+      </c>
+    </row>
+    <row r="100" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D100" s="4">
+        <v>280</v>
+      </c>
+      <c r="E100" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="F100" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G100" s="5">
+        <v>2</v>
+      </c>
+      <c r="H100" s="4">
+        <v>2</v>
+      </c>
+      <c r="I100" s="4">
+        <v>3</v>
+      </c>
+      <c r="J100" s="4">
+        <v>47.786822999999998</v>
+      </c>
+    </row>
+    <row r="101" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D101" s="3">
+        <v>240</v>
+      </c>
+      <c r="E101" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="F101" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="G101" s="6">
+        <v>1.75</v>
+      </c>
+      <c r="H101" s="3">
+        <v>2</v>
+      </c>
+      <c r="I101" s="3">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3">
+        <v>98.228806000000006</v>
+      </c>
+    </row>
+    <row r="102" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D102" s="4">
+        <v>240</v>
+      </c>
+      <c r="E102" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="F102" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G102" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="H102" s="4">
+        <v>0</v>
+      </c>
+      <c r="I102" s="4">
+        <v>5</v>
+      </c>
+      <c r="J102" s="4">
+        <v>24.220154000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="4:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="D103" s="3">
+        <v>280</v>
+      </c>
+      <c r="E103" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="F103" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="G103" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H103" s="3">
+        <v>2</v>
+      </c>
+      <c r="I103" s="3">
+        <v>6</v>
+      </c>
+      <c r="J103" s="3">
+        <v>38.463979999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Prusa Work/Adhesion Testing/Optimization Testing/Optimal Design Runs.xlsx
+++ b/Prusa Work/Adhesion Testing/Optimization Testing/Optimal Design Runs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github Stuff\Cylindrical-4th-Axis-Printer\Prusa Work\Adhesion Testing\Optimization Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC7F20C-57EC-4092-A71E-3D3C17F9A03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974C52BE-E97C-49C8-BC50-60A5F36E35D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>Run</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>Started taking pictures of post-break mesh</t>
+  </si>
+  <si>
+    <t>Validation Runs</t>
   </si>
 </sst>
 </file>
@@ -172,8 +175,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}" name="Table4" displayName="Table4" ref="B2:K104" totalsRowShown="0">
-  <autoFilter ref="B2:K104" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}" name="Table4" displayName="Table4" ref="B2:K116" totalsRowShown="0">
+  <autoFilter ref="B2:K116" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="19"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9C86E860-61AA-4FEE-8EB4-A30E954E2ABD}" name="Run" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{A20EC31A-F218-4399-BC4B-A51A407258CC}" name="Mandrel"/>
@@ -453,16 +462,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K104"/>
+  <dimension ref="B2:K116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="6.1015625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7890625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.1015625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.68359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.9453125" customWidth="1"/>
-    <col min="8" max="8" width="15.3125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.9453125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.3125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.05078125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.68359375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.20703125" bestFit="1" customWidth="1"/>
@@ -481,13 +490,13 @@
       <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I2" t="s">
@@ -500,7 +509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3">
         <v>1</v>
       </c>
@@ -513,13 +522,13 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>0.45</v>
-      </c>
-      <c r="G3">
-        <v>0.25</v>
-      </c>
-      <c r="H3">
+      <c r="F3" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H3" s="2">
         <v>1.75</v>
       </c>
       <c r="I3">
@@ -529,7 +538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4">
         <v>1</v>
       </c>
@@ -542,20 +551,20 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>0.45</v>
-      </c>
-      <c r="G4">
-        <v>0.25</v>
-      </c>
-      <c r="H4">
+      <c r="F4" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H4" s="2">
         <v>1.75</v>
       </c>
       <c r="I4">
         <v>73.643699999999995</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5">
         <v>1</v>
       </c>
@@ -568,20 +577,20 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>0.45</v>
-      </c>
-      <c r="G5">
-        <v>0.25</v>
-      </c>
-      <c r="H5">
+      <c r="F5" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H5" s="2">
         <v>1.75</v>
       </c>
       <c r="I5">
         <v>89.305999999999997</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6">
         <v>1</v>
       </c>
@@ -594,20 +603,20 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>0.45</v>
-      </c>
-      <c r="G6">
-        <v>0.25</v>
-      </c>
-      <c r="H6">
+      <c r="F6" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="2">
         <v>1.75</v>
       </c>
       <c r="I6">
         <v>73.695700000000002</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7">
         <v>1</v>
       </c>
@@ -620,20 +629,20 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7">
-        <v>0.45</v>
-      </c>
-      <c r="G7">
-        <v>0.25</v>
-      </c>
-      <c r="H7">
+      <c r="F7" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H7" s="2">
         <v>1.75</v>
       </c>
       <c r="I7">
         <v>48.312100000000001</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8">
         <v>1</v>
       </c>
@@ -646,20 +655,20 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8">
-        <v>0.45</v>
-      </c>
-      <c r="G8">
-        <v>0.25</v>
-      </c>
-      <c r="H8">
+      <c r="F8" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H8" s="2">
         <v>1.75</v>
       </c>
       <c r="I8">
         <v>85.577500000000001</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9">
         <v>2</v>
       </c>
@@ -672,13 +681,13 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9">
-        <v>0.45</v>
-      </c>
-      <c r="G9">
-        <v>0.25</v>
-      </c>
-      <c r="H9">
+      <c r="F9" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H9" s="2">
         <v>1.75</v>
       </c>
       <c r="I9">
@@ -688,7 +697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10">
         <v>2</v>
       </c>
@@ -701,20 +710,20 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10">
-        <v>0.45</v>
-      </c>
-      <c r="G10">
-        <v>0.25</v>
-      </c>
-      <c r="H10">
+      <c r="F10" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="2">
         <v>1.75</v>
       </c>
       <c r="I10">
         <v>100.43049999999999</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B11">
         <v>2</v>
       </c>
@@ -727,20 +736,20 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11">
-        <v>0.45</v>
-      </c>
-      <c r="G11">
-        <v>0.25</v>
-      </c>
-      <c r="H11">
+      <c r="F11" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H11" s="2">
         <v>1.75</v>
       </c>
       <c r="I11">
         <v>90.388499999999993</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12">
         <v>2</v>
       </c>
@@ -753,20 +762,20 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12">
-        <v>0.45</v>
-      </c>
-      <c r="G12">
-        <v>0.25</v>
-      </c>
-      <c r="H12">
+      <c r="F12" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H12" s="2">
         <v>1.75</v>
       </c>
       <c r="I12">
         <v>101.8031</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13">
         <v>2</v>
       </c>
@@ -779,20 +788,20 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13">
-        <v>0.45</v>
-      </c>
-      <c r="G13">
-        <v>0.25</v>
-      </c>
-      <c r="H13">
+      <c r="F13" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H13" s="2">
         <v>1.75</v>
       </c>
       <c r="I13">
         <v>62.641399999999997</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B14">
         <v>2</v>
       </c>
@@ -805,20 +814,20 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14">
-        <v>0.45</v>
-      </c>
-      <c r="G14">
-        <v>0.25</v>
-      </c>
-      <c r="H14">
+      <c r="F14" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H14" s="2">
         <v>1.75</v>
       </c>
       <c r="I14">
         <v>72.420699999999997</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15">
         <v>3</v>
       </c>
@@ -831,13 +840,13 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15">
-        <v>0.45</v>
-      </c>
-      <c r="G15">
-        <v>0.25</v>
-      </c>
-      <c r="H15">
+      <c r="F15" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H15" s="2">
         <v>1.75</v>
       </c>
       <c r="I15">
@@ -847,7 +856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B16">
         <v>3</v>
       </c>
@@ -860,20 +869,20 @@
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16">
-        <v>0.45</v>
-      </c>
-      <c r="G16">
-        <v>0.25</v>
-      </c>
-      <c r="H16">
+      <c r="F16" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H16" s="2">
         <v>1.75</v>
       </c>
       <c r="I16">
         <v>85.453800000000001</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B17">
         <v>3</v>
       </c>
@@ -886,20 +895,20 @@
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17">
-        <v>0.45</v>
-      </c>
-      <c r="G17">
-        <v>0.25</v>
-      </c>
-      <c r="H17">
+      <c r="F17" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H17" s="2">
         <v>1.75</v>
       </c>
       <c r="I17">
         <v>82.852099999999993</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18">
         <v>3</v>
       </c>
@@ -912,20 +921,20 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18">
-        <v>0.45</v>
-      </c>
-      <c r="G18">
-        <v>0.25</v>
-      </c>
-      <c r="H18">
+      <c r="F18" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H18" s="2">
         <v>1.75</v>
       </c>
       <c r="I18">
         <v>103.39100000000001</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B19">
         <v>3</v>
       </c>
@@ -938,20 +947,20 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19">
-        <v>0.45</v>
-      </c>
-      <c r="G19">
-        <v>0.25</v>
-      </c>
-      <c r="H19">
+      <c r="F19" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H19" s="2">
         <v>1.75</v>
       </c>
       <c r="I19">
         <v>59.873199999999997</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B20">
         <v>3</v>
       </c>
@@ -964,20 +973,20 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20">
-        <v>0.45</v>
-      </c>
-      <c r="G20">
-        <v>0.25</v>
-      </c>
-      <c r="H20">
+      <c r="F20" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H20" s="2">
         <v>1.75</v>
       </c>
       <c r="I20">
         <v>63.8598</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21">
         <v>4</v>
       </c>
@@ -990,20 +999,20 @@
       <c r="E21">
         <v>2</v>
       </c>
-      <c r="F21">
-        <v>0.2</v>
-      </c>
-      <c r="G21">
+      <c r="F21" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G21" s="2">
         <v>0.3</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>2</v>
       </c>
       <c r="I21">
         <v>58.163179999999997</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B22">
         <v>4</v>
       </c>
@@ -1016,20 +1025,20 @@
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22">
-        <v>0.45</v>
-      </c>
-      <c r="G22">
-        <v>0.25</v>
-      </c>
-      <c r="H22">
+      <c r="F22" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H22" s="2">
         <v>2</v>
       </c>
       <c r="I22">
         <v>73.379589999999993</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23">
         <v>4</v>
       </c>
@@ -1042,20 +1051,20 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23">
-        <v>0.2</v>
-      </c>
-      <c r="G23">
-        <v>0.25</v>
-      </c>
-      <c r="H23">
+      <c r="F23" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H23" s="2">
         <v>1.75</v>
       </c>
       <c r="I23">
         <v>71.820710000000005</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B24">
         <v>4</v>
       </c>
@@ -1068,20 +1077,20 @@
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>0.2</v>
-      </c>
-      <c r="G24">
-        <v>0.2</v>
-      </c>
-      <c r="H24">
+      <c r="F24" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H24" s="2">
         <v>1.75</v>
       </c>
       <c r="I24">
         <v>45.514893000000001</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B25">
         <v>4</v>
       </c>
@@ -1094,20 +1103,20 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25">
-        <v>0.45</v>
-      </c>
-      <c r="G25">
+      <c r="F25" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G25" s="2">
         <v>0.3</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>2</v>
       </c>
       <c r="I25">
         <v>49.046460000000003</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26">
         <v>4</v>
       </c>
@@ -1120,20 +1129,20 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26">
-        <v>0.2</v>
-      </c>
-      <c r="G26">
-        <v>0.25</v>
-      </c>
-      <c r="H26">
+      <c r="F26" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H26" s="2">
         <v>2</v>
       </c>
       <c r="I26">
         <v>90.490819999999999</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B27">
         <v>5</v>
       </c>
@@ -1146,20 +1155,20 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27">
-        <v>0.45</v>
-      </c>
-      <c r="G27">
-        <v>0.25</v>
-      </c>
-      <c r="H27">
+      <c r="F27" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H27" s="2">
         <v>1.75</v>
       </c>
       <c r="I27">
         <v>61.297767999999998</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B28">
         <v>5</v>
       </c>
@@ -1172,20 +1181,20 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28">
-        <v>0.2</v>
-      </c>
-      <c r="G28">
-        <v>0.2</v>
-      </c>
-      <c r="H28">
+      <c r="F28" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H28" s="2">
         <v>1.5</v>
       </c>
       <c r="I28">
         <v>27.887608</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B29">
         <v>5</v>
       </c>
@@ -1198,20 +1207,20 @@
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29">
-        <v>0.45</v>
-      </c>
-      <c r="G29">
-        <v>0.25</v>
-      </c>
-      <c r="H29">
+      <c r="F29" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H29" s="2">
         <v>2</v>
       </c>
       <c r="I29">
         <v>82.294780000000003</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B30">
         <v>5</v>
       </c>
@@ -1224,20 +1233,20 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="2">
         <v>0.7</v>
       </c>
-      <c r="G30">
-        <v>0.25</v>
-      </c>
-      <c r="H30">
+      <c r="G30" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H30" s="2">
         <v>2</v>
       </c>
       <c r="I30">
         <v>95.025509999999997</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B31">
         <v>5</v>
       </c>
@@ -1250,20 +1259,20 @@
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31">
-        <v>0.45</v>
-      </c>
-      <c r="G31">
-        <v>0.25</v>
-      </c>
-      <c r="H31">
+      <c r="F31" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H31" s="2">
         <v>1.75</v>
       </c>
       <c r="I31">
         <v>66.340900000000005</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B32">
         <v>5</v>
       </c>
@@ -1276,20 +1285,20 @@
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="F32">
-        <v>0.45</v>
-      </c>
-      <c r="G32">
-        <v>0.2</v>
-      </c>
-      <c r="H32">
+      <c r="F32" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H32" s="2">
         <v>1.75</v>
       </c>
       <c r="I32">
         <v>81.566479999999999</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B33">
         <v>6</v>
       </c>
@@ -1302,20 +1311,20 @@
       <c r="E33">
         <v>0</v>
       </c>
-      <c r="F33">
-        <v>0.45</v>
-      </c>
-      <c r="G33">
-        <v>0.25</v>
-      </c>
-      <c r="H33">
+      <c r="F33" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H33" s="2">
         <v>1.75</v>
       </c>
       <c r="I33">
         <v>65.366780000000006</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B34">
         <v>6</v>
       </c>
@@ -1328,20 +1337,20 @@
       <c r="E34">
         <v>1</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2">
         <v>0.7</v>
       </c>
-      <c r="G34">
-        <v>0.2</v>
-      </c>
-      <c r="H34">
+      <c r="G34" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H34" s="2">
         <v>2</v>
       </c>
       <c r="I34">
         <v>48.211280000000002</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B35">
         <v>6</v>
       </c>
@@ -1354,20 +1363,20 @@
       <c r="E35">
         <v>2</v>
       </c>
-      <c r="F35">
-        <v>0.45</v>
-      </c>
-      <c r="G35">
+      <c r="F35" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G35" s="2">
         <v>0.3</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="2">
         <v>1.5</v>
       </c>
       <c r="I35">
         <v>63.125390000000003</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B36">
         <v>6</v>
       </c>
@@ -1380,20 +1389,20 @@
       <c r="E36">
         <v>0</v>
       </c>
-      <c r="F36">
-        <v>0.2</v>
-      </c>
-      <c r="G36">
+      <c r="F36" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G36" s="2">
         <v>0.3</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="2">
         <v>1.75</v>
       </c>
       <c r="I36">
         <v>64.643060000000006</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B37">
         <v>6</v>
       </c>
@@ -1406,20 +1415,20 @@
       <c r="E37">
         <v>0</v>
       </c>
-      <c r="F37">
-        <v>0.2</v>
-      </c>
-      <c r="G37">
+      <c r="F37" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G37" s="2">
         <v>0.3</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="2">
         <v>2</v>
       </c>
       <c r="I37">
         <v>57.120350000000002</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B38">
         <v>6</v>
       </c>
@@ -1432,20 +1441,20 @@
       <c r="E38">
         <v>0</v>
       </c>
-      <c r="F38">
-        <v>0.2</v>
-      </c>
-      <c r="G38">
-        <v>0.2</v>
-      </c>
-      <c r="H38">
+      <c r="F38" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="2">
         <v>2</v>
       </c>
       <c r="I38">
         <v>42.58032</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B39">
         <v>7</v>
       </c>
@@ -1458,13 +1467,13 @@
       <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2">
         <v>0.7</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="2">
         <v>0.3</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="2">
         <v>2</v>
       </c>
       <c r="I39">
@@ -1474,7 +1483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B40">
         <v>7</v>
       </c>
@@ -1487,13 +1496,13 @@
       <c r="E40">
         <v>1</v>
       </c>
-      <c r="F40">
-        <v>0.2</v>
-      </c>
-      <c r="G40">
+      <c r="F40" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G40" s="2">
         <v>0.3</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="2">
         <v>2</v>
       </c>
       <c r="I40">
@@ -1503,7 +1512,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B41">
         <v>7</v>
       </c>
@@ -1516,20 +1525,20 @@
       <c r="E41">
         <v>1</v>
       </c>
-      <c r="F41">
-        <v>0.45</v>
-      </c>
-      <c r="G41">
-        <v>0.2</v>
-      </c>
-      <c r="H41">
+      <c r="F41" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H41" s="2">
         <v>1.75</v>
       </c>
       <c r="I41">
         <v>42.836829999999999</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B42">
         <v>7</v>
       </c>
@@ -1542,20 +1551,20 @@
       <c r="E42">
         <v>2</v>
       </c>
-      <c r="F42">
-        <v>0.2</v>
-      </c>
-      <c r="G42">
+      <c r="F42" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G42" s="2">
         <v>0.3</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="2">
         <v>1.75</v>
       </c>
       <c r="I42">
         <v>45.427864</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B43">
         <v>7</v>
       </c>
@@ -1568,20 +1577,20 @@
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="2">
         <v>0.7</v>
       </c>
-      <c r="G43">
-        <v>0.25</v>
-      </c>
-      <c r="H43">
+      <c r="G43" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H43" s="2">
         <v>1.75</v>
       </c>
       <c r="I43">
         <v>55.901940000000003</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B44">
         <v>7</v>
       </c>
@@ -1594,20 +1603,20 @@
       <c r="E44">
         <v>1</v>
       </c>
-      <c r="F44">
-        <v>0.45</v>
-      </c>
-      <c r="G44">
-        <v>0.25</v>
-      </c>
-      <c r="H44">
+      <c r="F44" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H44" s="2">
         <v>1.5</v>
       </c>
       <c r="I44">
         <v>45.398857</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45">
         <v>8</v>
       </c>
@@ -1620,20 +1629,20 @@
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="F45">
-        <v>0.2</v>
-      </c>
-      <c r="G45">
-        <v>0.25</v>
-      </c>
-      <c r="H45">
+      <c r="F45" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H45" s="2">
         <v>1.75</v>
       </c>
       <c r="I45">
         <v>55.978282999999998</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B46">
         <v>8</v>
       </c>
@@ -1646,20 +1655,20 @@
       <c r="E46">
         <v>1</v>
       </c>
-      <c r="F46">
-        <v>0.45</v>
-      </c>
-      <c r="G46">
-        <v>0.25</v>
-      </c>
-      <c r="H46">
+      <c r="F46" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H46" s="2">
         <v>1.5</v>
       </c>
       <c r="I46">
         <v>99.326599999999999</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B47">
         <v>8</v>
       </c>
@@ -1672,13 +1681,13 @@
       <c r="E47">
         <v>0</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="2">
         <v>0.7</v>
       </c>
-      <c r="G47">
-        <v>0.2</v>
-      </c>
-      <c r="H47">
+      <c r="G47" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H47" s="2">
         <v>1.5</v>
       </c>
       <c r="I47">
@@ -1688,7 +1697,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B48">
         <v>8</v>
       </c>
@@ -1701,20 +1710,20 @@
       <c r="E48">
         <v>2</v>
       </c>
-      <c r="F48">
-        <v>0.45</v>
-      </c>
-      <c r="G48">
-        <v>0.25</v>
-      </c>
-      <c r="H48">
+      <c r="F48" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H48" s="2">
         <v>1.5</v>
       </c>
       <c r="I48">
         <v>42.645977000000002</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B49">
         <v>8</v>
       </c>
@@ -1727,20 +1736,20 @@
       <c r="E49">
         <v>2</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="2">
         <v>0.7</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="2">
         <v>0.3</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="2">
         <v>1.75</v>
       </c>
       <c r="I49">
         <v>50.823695999999998</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B50">
         <v>8</v>
       </c>
@@ -1753,20 +1762,20 @@
       <c r="E50">
         <v>2</v>
       </c>
-      <c r="F50">
-        <v>0.2</v>
-      </c>
-      <c r="G50">
-        <v>0.2</v>
-      </c>
-      <c r="H50">
+      <c r="F50" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H50" s="2">
         <v>1.75</v>
       </c>
       <c r="I50">
         <v>92.132164000000003</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B51">
         <v>9</v>
       </c>
@@ -1779,20 +1788,20 @@
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="F51">
-        <v>0.45</v>
-      </c>
-      <c r="G51">
-        <v>0.25</v>
-      </c>
-      <c r="H51">
+      <c r="F51" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H51" s="2">
         <v>1.75</v>
       </c>
       <c r="I51">
         <v>51.168754999999997</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B52">
         <v>9</v>
       </c>
@@ -1805,20 +1814,20 @@
       <c r="E52">
         <v>0</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="2">
         <v>0.7</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="2">
         <v>0.3</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="2">
         <v>1.75</v>
       </c>
       <c r="I52">
         <v>65.939350000000005</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B53">
         <v>9</v>
       </c>
@@ -1831,20 +1840,20 @@
       <c r="E53">
         <v>1</v>
       </c>
-      <c r="F53">
-        <v>0.45</v>
-      </c>
-      <c r="G53">
-        <v>0.2</v>
-      </c>
-      <c r="H53">
+      <c r="F53" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G53" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H53" s="2">
         <v>1.75</v>
       </c>
       <c r="I53">
         <v>64.252189999999999</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B54">
         <v>9</v>
       </c>
@@ -1857,20 +1866,20 @@
       <c r="E54">
         <v>1</v>
       </c>
-      <c r="F54">
-        <v>0.45</v>
-      </c>
-      <c r="G54">
-        <v>0.2</v>
-      </c>
-      <c r="H54">
+      <c r="F54" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G54" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H54" s="2">
         <v>1.5</v>
       </c>
       <c r="I54">
         <v>76.228675999999993</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B55">
         <v>9</v>
       </c>
@@ -1883,20 +1892,20 @@
       <c r="E55">
         <v>2</v>
       </c>
-      <c r="F55">
-        <v>0.2</v>
-      </c>
-      <c r="G55">
-        <v>0.2</v>
-      </c>
-      <c r="H55">
+      <c r="F55" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H55" s="2">
         <v>2</v>
       </c>
       <c r="I55">
         <v>42.958973</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B56">
         <v>9</v>
       </c>
@@ -1909,20 +1918,20 @@
       <c r="E56">
         <v>1</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="2">
         <v>0.7</v>
       </c>
-      <c r="G56">
-        <v>0.25</v>
-      </c>
-      <c r="H56">
+      <c r="G56" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H56" s="2">
         <v>1.75</v>
       </c>
       <c r="I56">
         <v>66.652373999999995</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B57">
         <v>10</v>
       </c>
@@ -1935,20 +1944,20 @@
       <c r="E57">
         <v>2</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="2">
         <v>0.7</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="2">
         <v>0.3</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="2">
         <v>1.75</v>
       </c>
       <c r="I57">
         <v>50.625205999999999</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B58">
         <v>10</v>
       </c>
@@ -1961,20 +1970,20 @@
       <c r="E58">
         <v>0</v>
       </c>
-      <c r="F58">
-        <v>0.2</v>
-      </c>
-      <c r="G58">
-        <v>0.2</v>
-      </c>
-      <c r="H58">
+      <c r="F58" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G58" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H58" s="2">
         <v>1.5</v>
       </c>
       <c r="I58">
         <v>26.986775999999999</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B59">
         <v>10</v>
       </c>
@@ -1987,20 +1996,20 @@
       <c r="E59">
         <v>0</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="2">
         <v>0.7</v>
       </c>
-      <c r="G59">
-        <v>0.2</v>
-      </c>
-      <c r="H59">
+      <c r="G59" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H59" s="2">
         <v>1.5</v>
       </c>
       <c r="I59">
         <v>86.737859999999998</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B60">
         <v>10</v>
       </c>
@@ -2013,20 +2022,20 @@
       <c r="E60">
         <v>2</v>
       </c>
-      <c r="F60">
-        <v>0.45</v>
-      </c>
-      <c r="G60">
-        <v>0.25</v>
-      </c>
-      <c r="H60">
+      <c r="F60" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G60" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H60" s="2">
         <v>1.75</v>
       </c>
       <c r="I60">
         <v>85.203400000000002</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B61">
         <v>10</v>
       </c>
@@ -2039,20 +2048,20 @@
       <c r="E61">
         <v>2</v>
       </c>
-      <c r="F61">
-        <v>0.2</v>
-      </c>
-      <c r="G61">
-        <v>0.25</v>
-      </c>
-      <c r="H61">
+      <c r="F61" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G61" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H61" s="2">
         <v>1.5</v>
       </c>
       <c r="I61">
         <v>34.509483000000003</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B62">
         <v>10</v>
       </c>
@@ -2065,20 +2074,20 @@
       <c r="E62">
         <v>0</v>
       </c>
-      <c r="F62">
-        <v>0.2</v>
-      </c>
-      <c r="G62">
+      <c r="F62" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G62" s="2">
         <v>0.3</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="2">
         <v>1.5</v>
       </c>
       <c r="I62">
         <v>42.255108</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B63">
         <v>11</v>
       </c>
@@ -2091,20 +2100,20 @@
       <c r="E63">
         <v>2</v>
       </c>
-      <c r="F63">
-        <v>0.45</v>
-      </c>
-      <c r="G63">
-        <v>0.2</v>
-      </c>
-      <c r="H63">
+      <c r="F63" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G63" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H63" s="2">
         <v>2</v>
       </c>
       <c r="I63">
         <v>64.363650000000007</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B64">
         <v>11</v>
       </c>
@@ -2117,20 +2126,20 @@
       <c r="E64">
         <v>0</v>
       </c>
-      <c r="F64">
-        <v>0.45</v>
-      </c>
-      <c r="G64">
-        <v>0.25</v>
-      </c>
-      <c r="H64">
+      <c r="F64" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G64" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H64" s="2">
         <v>1.75</v>
       </c>
       <c r="I64">
         <v>73.243706000000003</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B65">
         <v>11</v>
       </c>
@@ -2143,20 +2152,20 @@
       <c r="E65">
         <v>0</v>
       </c>
-      <c r="F65">
-        <v>0.2</v>
-      </c>
-      <c r="G65">
+      <c r="F65" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G65" s="2">
         <v>0.3</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="2">
         <v>1.5</v>
       </c>
       <c r="I65">
         <v>44.737735999999998</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B66">
         <v>11</v>
       </c>
@@ -2169,20 +2178,20 @@
       <c r="E66">
         <v>0</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="2">
         <v>0.7</v>
       </c>
-      <c r="G66">
-        <v>0.25</v>
-      </c>
-      <c r="H66">
+      <c r="G66" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H66" s="2">
         <v>1.5</v>
       </c>
       <c r="I66">
         <v>53.043709999999997</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B67">
         <v>11</v>
       </c>
@@ -2195,20 +2204,20 @@
       <c r="E67">
         <v>0</v>
       </c>
-      <c r="F67">
-        <v>0.45</v>
-      </c>
-      <c r="G67">
-        <v>0.25</v>
-      </c>
-      <c r="H67">
+      <c r="F67" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H67" s="2">
         <v>1.75</v>
       </c>
       <c r="I67">
         <v>49.573214999999998</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B68">
         <v>11</v>
       </c>
@@ -2221,20 +2230,20 @@
       <c r="E68">
         <v>2</v>
       </c>
-      <c r="F68">
-        <v>0.45</v>
-      </c>
-      <c r="G68">
-        <v>0.25</v>
-      </c>
-      <c r="H68">
+      <c r="F68" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H68" s="2">
         <v>2</v>
       </c>
       <c r="I68">
         <v>41.270297999999997</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B69">
         <v>12</v>
       </c>
@@ -2247,20 +2256,20 @@
       <c r="E69">
         <v>1</v>
       </c>
-      <c r="F69">
-        <v>0.2</v>
-      </c>
-      <c r="G69">
-        <v>0.25</v>
-      </c>
-      <c r="H69">
+      <c r="F69" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H69" s="2">
         <v>1.5</v>
       </c>
       <c r="I69">
         <v>56.098903999999997</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B70">
         <v>12</v>
       </c>
@@ -2273,20 +2282,20 @@
       <c r="E70">
         <v>2</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="2">
         <v>0.7</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="2">
         <v>0.3</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="2">
         <v>1.5</v>
       </c>
       <c r="I70">
         <v>44.398777000000003</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B71">
         <v>12</v>
       </c>
@@ -2299,20 +2308,20 @@
       <c r="E71">
         <v>0</v>
       </c>
-      <c r="F71">
-        <v>0.2</v>
-      </c>
-      <c r="G71">
-        <v>0.25</v>
-      </c>
-      <c r="H71">
+      <c r="F71" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G71" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H71" s="2">
         <v>2</v>
       </c>
       <c r="I71">
         <v>43.522379999999998</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72">
         <v>12</v>
       </c>
@@ -2325,20 +2334,20 @@
       <c r="E72">
         <v>1</v>
       </c>
-      <c r="F72">
-        <v>0.45</v>
-      </c>
-      <c r="G72">
+      <c r="F72" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G72" s="2">
         <v>0.3</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="2">
         <v>2</v>
       </c>
       <c r="I72">
         <v>56.187457999999999</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B73">
         <v>12</v>
       </c>
@@ -2351,20 +2360,20 @@
       <c r="E73">
         <v>0</v>
       </c>
-      <c r="F73">
-        <v>0.2</v>
-      </c>
-      <c r="G73">
-        <v>0.2</v>
-      </c>
-      <c r="H73">
+      <c r="F73" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G73" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="2">
         <v>1.5</v>
       </c>
       <c r="I73">
         <v>49.915230000000001</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B74">
         <v>12</v>
       </c>
@@ -2377,20 +2386,20 @@
       <c r="E74">
         <v>0</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="2">
         <v>0.7</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="2">
         <v>0.3</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="2">
         <v>2</v>
       </c>
       <c r="I74">
         <v>49.525886999999997</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B75">
         <v>13</v>
       </c>
@@ -2403,20 +2412,20 @@
       <c r="E75">
         <v>0</v>
       </c>
-      <c r="F75">
-        <v>0.2</v>
-      </c>
-      <c r="G75">
-        <v>0.2</v>
-      </c>
-      <c r="H75">
+      <c r="F75" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G75" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H75" s="2">
         <v>2</v>
       </c>
       <c r="I75">
         <v>106.62945000000001</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B76">
         <v>13</v>
       </c>
@@ -2429,20 +2438,20 @@
       <c r="E76">
         <v>0</v>
       </c>
-      <c r="F76">
-        <v>0.45</v>
-      </c>
-      <c r="G76">
-        <v>0.25</v>
-      </c>
-      <c r="H76">
+      <c r="F76" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G76" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H76" s="2">
         <v>1.75</v>
       </c>
       <c r="I76">
         <v>88.038730000000001</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B77">
         <v>13</v>
       </c>
@@ -2455,20 +2464,20 @@
       <c r="E77">
         <v>1</v>
       </c>
-      <c r="F77">
-        <v>0.2</v>
-      </c>
-      <c r="G77">
-        <v>0.25</v>
-      </c>
-      <c r="H77">
+      <c r="F77" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G77" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H77" s="2">
         <v>1.75</v>
       </c>
       <c r="I77">
         <v>55.057602000000003</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B78">
         <v>13</v>
       </c>
@@ -2481,20 +2490,20 @@
       <c r="E78">
         <v>0</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="2">
         <v>0.7</v>
       </c>
-      <c r="G78">
-        <v>0.2</v>
-      </c>
-      <c r="H78">
+      <c r="G78" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H78" s="2">
         <v>2</v>
       </c>
       <c r="I78">
         <v>49.835830000000001</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B79">
         <v>13</v>
       </c>
@@ -2507,20 +2516,20 @@
       <c r="E79">
         <v>1</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="2">
         <v>0.7</v>
       </c>
-      <c r="G79">
-        <v>0.25</v>
-      </c>
-      <c r="H79">
+      <c r="G79" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H79" s="2">
         <v>1.75</v>
       </c>
       <c r="I79">
         <v>46.455419999999997</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B80">
         <v>13</v>
       </c>
@@ -2533,20 +2542,20 @@
       <c r="E80">
         <v>2</v>
       </c>
-      <c r="F80">
-        <v>0.45</v>
-      </c>
-      <c r="G80">
-        <v>0.25</v>
-      </c>
-      <c r="H80">
+      <c r="F80" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G80" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H80" s="2">
         <v>2</v>
       </c>
       <c r="I80">
         <v>52.750557000000001</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B81">
         <v>14</v>
       </c>
@@ -2559,20 +2568,20 @@
       <c r="E81">
         <v>0</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="2">
         <v>0.7</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="2">
         <v>0.3</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="2">
         <v>1.5</v>
       </c>
       <c r="I81">
         <v>48.605206000000003</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B82">
         <v>14</v>
       </c>
@@ -2585,20 +2594,20 @@
       <c r="E82">
         <v>2</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="2">
         <v>0.7</v>
       </c>
-      <c r="G82">
-        <v>0.2</v>
-      </c>
-      <c r="H82">
+      <c r="G82" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H82" s="2">
         <v>2</v>
       </c>
       <c r="I82">
         <v>109.57774999999999</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B83">
         <v>14</v>
       </c>
@@ -2611,20 +2620,20 @@
       <c r="E83">
         <v>2</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="2">
         <v>0.7</v>
       </c>
-      <c r="G83">
-        <v>0.25</v>
-      </c>
-      <c r="H83">
+      <c r="G83" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H83" s="2">
         <v>2</v>
       </c>
       <c r="I83">
         <v>101.58937</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B84">
         <v>14</v>
       </c>
@@ -2637,20 +2646,20 @@
       <c r="E84">
         <v>1</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="2">
         <v>0.7</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="2">
         <v>0.3</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="2">
         <v>1.5</v>
       </c>
       <c r="I84">
         <v>55.442363999999998</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B85">
         <v>14</v>
       </c>
@@ -2663,20 +2672,20 @@
       <c r="E85">
         <v>0</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="2">
         <v>0.7</v>
       </c>
-      <c r="G85">
-        <v>0.2</v>
-      </c>
-      <c r="H85">
+      <c r="G85" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H85" s="2">
         <v>2</v>
       </c>
       <c r="I85">
         <v>96.187430000000006</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B86">
         <v>14</v>
       </c>
@@ -2689,20 +2698,20 @@
       <c r="E86">
         <v>2</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="2">
         <v>0.7</v>
       </c>
-      <c r="G86">
-        <v>0.2</v>
-      </c>
-      <c r="H86">
+      <c r="G86" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H86" s="2">
         <v>1.5</v>
       </c>
       <c r="I86">
         <v>35.883629999999997</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B87">
         <v>15</v>
       </c>
@@ -2715,20 +2724,20 @@
       <c r="E87">
         <v>2</v>
       </c>
-      <c r="F87">
-        <v>0.2</v>
-      </c>
-      <c r="G87">
+      <c r="F87" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G87" s="2">
         <v>0.3</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="2">
         <v>2</v>
       </c>
       <c r="I87">
         <v>99.925124999999994</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B88">
         <v>15</v>
       </c>
@@ -2741,20 +2750,20 @@
       <c r="E88">
         <v>2</v>
       </c>
-      <c r="F88">
-        <v>0.2</v>
-      </c>
-      <c r="G88">
-        <v>0.25</v>
-      </c>
-      <c r="H88">
+      <c r="F88" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G88" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H88" s="2">
         <v>1.75</v>
       </c>
       <c r="I88">
         <v>43.9163</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B89">
         <v>15</v>
       </c>
@@ -2767,20 +2776,20 @@
       <c r="E89">
         <v>1</v>
       </c>
-      <c r="F89">
-        <v>0.45</v>
-      </c>
-      <c r="G89">
+      <c r="F89" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G89" s="2">
         <v>0.3</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="2">
         <v>1.75</v>
       </c>
       <c r="I89">
         <v>48.215865999999998</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B90">
         <v>15</v>
       </c>
@@ -2793,20 +2802,20 @@
       <c r="E90">
         <v>2</v>
       </c>
-      <c r="F90">
-        <v>0.2</v>
-      </c>
-      <c r="G90">
-        <v>0.2</v>
-      </c>
-      <c r="H90">
+      <c r="F90" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H90" s="2">
         <v>2</v>
       </c>
       <c r="I90">
         <v>124.18344999999999</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B91">
         <v>15</v>
       </c>
@@ -2819,20 +2828,20 @@
       <c r="E91">
         <v>1</v>
       </c>
-      <c r="F91">
-        <v>0.45</v>
-      </c>
-      <c r="G91">
+      <c r="F91" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G91" s="2">
         <v>0.3</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="2">
         <v>1.5</v>
       </c>
       <c r="I91">
         <v>49.113639999999997</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B92">
         <v>15</v>
       </c>
@@ -2845,20 +2854,20 @@
       <c r="E92">
         <v>1</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="2">
         <v>0.7</v>
       </c>
-      <c r="G92">
-        <v>0.25</v>
-      </c>
-      <c r="H92">
+      <c r="G92" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H92" s="2">
         <v>1.75</v>
       </c>
       <c r="I92">
         <v>66.881399999999999</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="1">
         <v>16</v>
       </c>
@@ -2884,7 +2893,7 @@
         <v>112.68944500000001</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="1">
         <v>16</v>
       </c>
@@ -2910,7 +2919,7 @@
         <v>38.494520000000001</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="1">
         <v>16</v>
       </c>
@@ -2936,7 +2945,7 @@
         <v>36.946303999999998</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="1">
         <v>16</v>
       </c>
@@ -2962,7 +2971,7 @@
         <v>68.568550000000002</v>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="1">
         <v>16</v>
       </c>
@@ -2988,7 +2997,7 @@
         <v>54.046840000000003</v>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="1">
         <v>16</v>
       </c>
@@ -3014,7 +3023,7 @@
         <v>53.924689999999998</v>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="1">
         <v>17</v>
       </c>
@@ -3040,7 +3049,7 @@
         <v>56.175243000000002</v>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="1">
         <v>17</v>
       </c>
@@ -3066,7 +3075,7 @@
         <v>87.840230000000005</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="1">
         <v>17</v>
       </c>
@@ -3092,7 +3101,7 @@
         <v>47.786822999999998</v>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="1">
         <v>17</v>
       </c>
@@ -3118,7 +3127,7 @@
         <v>98.228806000000006</v>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="1">
         <v>17</v>
       </c>
@@ -3144,7 +3153,7 @@
         <v>24.220154000000001</v>
       </c>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="1">
         <v>17</v>
       </c>
@@ -3168,6 +3177,288 @@
       </c>
       <c r="I104">
         <v>38.463979999999999</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" s="1">
+        <v>18</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>240</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G105" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H105" s="2">
+        <v>2</v>
+      </c>
+      <c r="K105" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" s="1">
+        <v>18</v>
+      </c>
+      <c r="C106">
+        <v>2</v>
+      </c>
+      <c r="D106">
+        <v>240</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G106" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H106" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" s="1">
+        <v>18</v>
+      </c>
+      <c r="C107">
+        <v>3</v>
+      </c>
+      <c r="D107">
+        <v>240</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G107" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H107" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" s="1">
+        <v>18</v>
+      </c>
+      <c r="C108">
+        <v>4</v>
+      </c>
+      <c r="D108">
+        <v>240</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G108" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H108" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" s="1">
+        <v>18</v>
+      </c>
+      <c r="C109">
+        <v>5</v>
+      </c>
+      <c r="D109">
+        <v>240</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G109" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H109" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="1">
+        <v>18</v>
+      </c>
+      <c r="C110">
+        <v>6</v>
+      </c>
+      <c r="D110">
+        <v>240</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G110" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H110" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" s="1">
+        <v>19</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <v>240</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G111" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H111" s="2">
+        <v>2</v>
+      </c>
+      <c r="K111" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="1">
+        <v>19</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112">
+        <v>240</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G112" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H112" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" s="1">
+        <v>19</v>
+      </c>
+      <c r="C113">
+        <v>3</v>
+      </c>
+      <c r="D113">
+        <v>240</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G113" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H113" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" s="1">
+        <v>19</v>
+      </c>
+      <c r="C114">
+        <v>4</v>
+      </c>
+      <c r="D114">
+        <v>240</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G114" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H114" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" s="1">
+        <v>19</v>
+      </c>
+      <c r="C115">
+        <v>5</v>
+      </c>
+      <c r="D115">
+        <v>240</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G115" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H115" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" s="1">
+        <v>19</v>
+      </c>
+      <c r="C116">
+        <v>6</v>
+      </c>
+      <c r="D116">
+        <v>240</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="G116" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H116" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Prusa Work/Adhesion Testing/Optimization Testing/Optimal Design Runs.xlsx
+++ b/Prusa Work/Adhesion Testing/Optimization Testing/Optimal Design Runs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github Stuff\Cylindrical-4th-Axis-Printer\Prusa Work\Adhesion Testing\Optimization Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974C52BE-E97C-49C8-BC50-60A5F36E35D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E5C300-9389-49D3-A7AE-82C78CF01166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -176,13 +176,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}" name="Table4" displayName="Table4" ref="B2:K116" totalsRowShown="0">
-  <autoFilter ref="B2:K116" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="19"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B2:K116" xr:uid="{FBC1B571-4B51-41CD-ADCE-1AB837F4C666}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9C86E860-61AA-4FEE-8EB4-A30E954E2ABD}" name="Run" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{A20EC31A-F218-4399-BC4B-A51A407258CC}" name="Mandrel"/>
@@ -509,7 +503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B3">
         <v>1</v>
       </c>
@@ -538,7 +532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B4">
         <v>1</v>
       </c>
@@ -564,7 +558,7 @@
         <v>73.643699999999995</v>
       </c>
     </row>
-    <row r="5" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B5">
         <v>1</v>
       </c>
@@ -590,7 +584,7 @@
         <v>89.305999999999997</v>
       </c>
     </row>
-    <row r="6" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B6">
         <v>1</v>
       </c>
@@ -616,7 +610,7 @@
         <v>73.695700000000002</v>
       </c>
     </row>
-    <row r="7" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B7">
         <v>1</v>
       </c>
@@ -642,7 +636,7 @@
         <v>48.312100000000001</v>
       </c>
     </row>
-    <row r="8" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B8">
         <v>1</v>
       </c>
@@ -668,7 +662,7 @@
         <v>85.577500000000001</v>
       </c>
     </row>
-    <row r="9" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B9">
         <v>2</v>
       </c>
@@ -697,7 +691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B10">
         <v>2</v>
       </c>
@@ -723,7 +717,7 @@
         <v>100.43049999999999</v>
       </c>
     </row>
-    <row r="11" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B11">
         <v>2</v>
       </c>
@@ -749,7 +743,7 @@
         <v>90.388499999999993</v>
       </c>
     </row>
-    <row r="12" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B12">
         <v>2</v>
       </c>
@@ -775,7 +769,7 @@
         <v>101.8031</v>
       </c>
     </row>
-    <row r="13" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B13">
         <v>2</v>
       </c>
@@ -801,7 +795,7 @@
         <v>62.641399999999997</v>
       </c>
     </row>
-    <row r="14" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B14">
         <v>2</v>
       </c>
@@ -827,7 +821,7 @@
         <v>72.420699999999997</v>
       </c>
     </row>
-    <row r="15" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B15">
         <v>3</v>
       </c>
@@ -856,7 +850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B16">
         <v>3</v>
       </c>
@@ -882,7 +876,7 @@
         <v>85.453800000000001</v>
       </c>
     </row>
-    <row r="17" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B17">
         <v>3</v>
       </c>
@@ -908,7 +902,7 @@
         <v>82.852099999999993</v>
       </c>
     </row>
-    <row r="18" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B18">
         <v>3</v>
       </c>
@@ -934,7 +928,7 @@
         <v>103.39100000000001</v>
       </c>
     </row>
-    <row r="19" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B19">
         <v>3</v>
       </c>
@@ -960,7 +954,7 @@
         <v>59.873199999999997</v>
       </c>
     </row>
-    <row r="20" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B20">
         <v>3</v>
       </c>
@@ -986,7 +980,7 @@
         <v>63.8598</v>
       </c>
     </row>
-    <row r="21" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B21">
         <v>4</v>
       </c>
@@ -1012,7 +1006,7 @@
         <v>58.163179999999997</v>
       </c>
     </row>
-    <row r="22" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B22">
         <v>4</v>
       </c>
@@ -1038,7 +1032,7 @@
         <v>73.379589999999993</v>
       </c>
     </row>
-    <row r="23" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B23">
         <v>4</v>
       </c>
@@ -1064,7 +1058,7 @@
         <v>71.820710000000005</v>
       </c>
     </row>
-    <row r="24" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B24">
         <v>4</v>
       </c>
@@ -1090,7 +1084,7 @@
         <v>45.514893000000001</v>
       </c>
     </row>
-    <row r="25" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B25">
         <v>4</v>
       </c>
@@ -1116,7 +1110,7 @@
         <v>49.046460000000003</v>
       </c>
     </row>
-    <row r="26" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B26">
         <v>4</v>
       </c>
@@ -1142,7 +1136,7 @@
         <v>90.490819999999999</v>
       </c>
     </row>
-    <row r="27" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B27">
         <v>5</v>
       </c>
@@ -1168,7 +1162,7 @@
         <v>61.297767999999998</v>
       </c>
     </row>
-    <row r="28" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B28">
         <v>5</v>
       </c>
@@ -1194,7 +1188,7 @@
         <v>27.887608</v>
       </c>
     </row>
-    <row r="29" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B29">
         <v>5</v>
       </c>
@@ -1220,7 +1214,7 @@
         <v>82.294780000000003</v>
       </c>
     </row>
-    <row r="30" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B30">
         <v>5</v>
       </c>
@@ -1246,7 +1240,7 @@
         <v>95.025509999999997</v>
       </c>
     </row>
-    <row r="31" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B31">
         <v>5</v>
       </c>
@@ -1272,7 +1266,7 @@
         <v>66.340900000000005</v>
       </c>
     </row>
-    <row r="32" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B32">
         <v>5</v>
       </c>
@@ -1298,7 +1292,7 @@
         <v>81.566479999999999</v>
       </c>
     </row>
-    <row r="33" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B33">
         <v>6</v>
       </c>
@@ -1324,7 +1318,7 @@
         <v>65.366780000000006</v>
       </c>
     </row>
-    <row r="34" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B34">
         <v>6</v>
       </c>
@@ -1350,7 +1344,7 @@
         <v>48.211280000000002</v>
       </c>
     </row>
-    <row r="35" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B35">
         <v>6</v>
       </c>
@@ -1376,7 +1370,7 @@
         <v>63.125390000000003</v>
       </c>
     </row>
-    <row r="36" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B36">
         <v>6</v>
       </c>
@@ -1402,7 +1396,7 @@
         <v>64.643060000000006</v>
       </c>
     </row>
-    <row r="37" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B37">
         <v>6</v>
       </c>
@@ -1428,7 +1422,7 @@
         <v>57.120350000000002</v>
       </c>
     </row>
-    <row r="38" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B38">
         <v>6</v>
       </c>
@@ -1454,7 +1448,7 @@
         <v>42.58032</v>
       </c>
     </row>
-    <row r="39" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B39">
         <v>7</v>
       </c>
@@ -1483,7 +1477,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B40">
         <v>7</v>
       </c>
@@ -1512,7 +1506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B41">
         <v>7</v>
       </c>
@@ -1538,7 +1532,7 @@
         <v>42.836829999999999</v>
       </c>
     </row>
-    <row r="42" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B42">
         <v>7</v>
       </c>
@@ -1564,7 +1558,7 @@
         <v>45.427864</v>
       </c>
     </row>
-    <row r="43" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B43">
         <v>7</v>
       </c>
@@ -1590,7 +1584,7 @@
         <v>55.901940000000003</v>
       </c>
     </row>
-    <row r="44" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B44">
         <v>7</v>
       </c>
@@ -1616,7 +1610,7 @@
         <v>45.398857</v>
       </c>
     </row>
-    <row r="45" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B45">
         <v>8</v>
       </c>
@@ -1642,7 +1636,7 @@
         <v>55.978282999999998</v>
       </c>
     </row>
-    <row r="46" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B46">
         <v>8</v>
       </c>
@@ -1668,7 +1662,7 @@
         <v>99.326599999999999</v>
       </c>
     </row>
-    <row r="47" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B47">
         <v>8</v>
       </c>
@@ -1697,7 +1691,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="2:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B48">
         <v>8</v>
       </c>
@@ -1723,7 +1717,7 @@
         <v>42.645977000000002</v>
       </c>
     </row>
-    <row r="49" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B49">
         <v>8</v>
       </c>
@@ -1749,7 +1743,7 @@
         <v>50.823695999999998</v>
       </c>
     </row>
-    <row r="50" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B50">
         <v>8</v>
       </c>
@@ -1775,7 +1769,7 @@
         <v>92.132164000000003</v>
       </c>
     </row>
-    <row r="51" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B51">
         <v>9</v>
       </c>
@@ -1801,7 +1795,7 @@
         <v>51.168754999999997</v>
       </c>
     </row>
-    <row r="52" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B52">
         <v>9</v>
       </c>
@@ -1827,7 +1821,7 @@
         <v>65.939350000000005</v>
       </c>
     </row>
-    <row r="53" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B53">
         <v>9</v>
       </c>
@@ -1853,7 +1847,7 @@
         <v>64.252189999999999</v>
       </c>
     </row>
-    <row r="54" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B54">
         <v>9</v>
       </c>
@@ -1879,7 +1873,7 @@
         <v>76.228675999999993</v>
       </c>
     </row>
-    <row r="55" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B55">
         <v>9</v>
       </c>
@@ -1905,7 +1899,7 @@
         <v>42.958973</v>
       </c>
     </row>
-    <row r="56" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B56">
         <v>9</v>
       </c>
@@ -1931,7 +1925,7 @@
         <v>66.652373999999995</v>
       </c>
     </row>
-    <row r="57" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B57">
         <v>10</v>
       </c>
@@ -1957,7 +1951,7 @@
         <v>50.625205999999999</v>
       </c>
     </row>
-    <row r="58" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B58">
         <v>10</v>
       </c>
@@ -1983,7 +1977,7 @@
         <v>26.986775999999999</v>
       </c>
     </row>
-    <row r="59" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B59">
         <v>10</v>
       </c>
@@ -2009,7 +2003,7 @@
         <v>86.737859999999998</v>
       </c>
     </row>
-    <row r="60" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B60">
         <v>10</v>
       </c>
@@ -2035,7 +2029,7 @@
         <v>85.203400000000002</v>
       </c>
     </row>
-    <row r="61" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B61">
         <v>10</v>
       </c>
@@ -2061,7 +2055,7 @@
         <v>34.509483000000003</v>
       </c>
     </row>
-    <row r="62" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B62">
         <v>10</v>
       </c>
@@ -2087,7 +2081,7 @@
         <v>42.255108</v>
       </c>
     </row>
-    <row r="63" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B63">
         <v>11</v>
       </c>
@@ -2113,7 +2107,7 @@
         <v>64.363650000000007</v>
       </c>
     </row>
-    <row r="64" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B64">
         <v>11</v>
       </c>
@@ -2139,7 +2133,7 @@
         <v>73.243706000000003</v>
       </c>
     </row>
-    <row r="65" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B65">
         <v>11</v>
       </c>
@@ -2165,7 +2159,7 @@
         <v>44.737735999999998</v>
       </c>
     </row>
-    <row r="66" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B66">
         <v>11</v>
       </c>
@@ -2191,7 +2185,7 @@
         <v>53.043709999999997</v>
       </c>
     </row>
-    <row r="67" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B67">
         <v>11</v>
       </c>
@@ -2217,7 +2211,7 @@
         <v>49.573214999999998</v>
       </c>
     </row>
-    <row r="68" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B68">
         <v>11</v>
       </c>
@@ -2243,7 +2237,7 @@
         <v>41.270297999999997</v>
       </c>
     </row>
-    <row r="69" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B69">
         <v>12</v>
       </c>
@@ -2269,7 +2263,7 @@
         <v>56.098903999999997</v>
       </c>
     </row>
-    <row r="70" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B70">
         <v>12</v>
       </c>
@@ -2295,7 +2289,7 @@
         <v>44.398777000000003</v>
       </c>
     </row>
-    <row r="71" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B71">
         <v>12</v>
       </c>
@@ -2321,7 +2315,7 @@
         <v>43.522379999999998</v>
       </c>
     </row>
-    <row r="72" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B72">
         <v>12</v>
       </c>
@@ -2347,7 +2341,7 @@
         <v>56.187457999999999</v>
       </c>
     </row>
-    <row r="73" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B73">
         <v>12</v>
       </c>
@@ -2373,7 +2367,7 @@
         <v>49.915230000000001</v>
       </c>
     </row>
-    <row r="74" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B74">
         <v>12</v>
       </c>
@@ -2399,7 +2393,7 @@
         <v>49.525886999999997</v>
       </c>
     </row>
-    <row r="75" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B75">
         <v>13</v>
       </c>
@@ -2425,7 +2419,7 @@
         <v>106.62945000000001</v>
       </c>
     </row>
-    <row r="76" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B76">
         <v>13</v>
       </c>
@@ -2451,7 +2445,7 @@
         <v>88.038730000000001</v>
       </c>
     </row>
-    <row r="77" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B77">
         <v>13</v>
       </c>
@@ -2477,7 +2471,7 @@
         <v>55.057602000000003</v>
       </c>
     </row>
-    <row r="78" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B78">
         <v>13</v>
       </c>
@@ -2503,7 +2497,7 @@
         <v>49.835830000000001</v>
       </c>
     </row>
-    <row r="79" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B79">
         <v>13</v>
       </c>
@@ -2529,7 +2523,7 @@
         <v>46.455419999999997</v>
       </c>
     </row>
-    <row r="80" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B80">
         <v>13</v>
       </c>
@@ -2555,7 +2549,7 @@
         <v>52.750557000000001</v>
       </c>
     </row>
-    <row r="81" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B81">
         <v>14</v>
       </c>
@@ -2581,7 +2575,7 @@
         <v>48.605206000000003</v>
       </c>
     </row>
-    <row r="82" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B82">
         <v>14</v>
       </c>
@@ -2607,7 +2601,7 @@
         <v>109.57774999999999</v>
       </c>
     </row>
-    <row r="83" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B83">
         <v>14</v>
       </c>
@@ -2633,7 +2627,7 @@
         <v>101.58937</v>
       </c>
     </row>
-    <row r="84" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B84">
         <v>14</v>
       </c>
@@ -2659,7 +2653,7 @@
         <v>55.442363999999998</v>
       </c>
     </row>
-    <row r="85" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B85">
         <v>14</v>
       </c>
@@ -2685,7 +2679,7 @@
         <v>96.187430000000006</v>
       </c>
     </row>
-    <row r="86" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B86">
         <v>14</v>
       </c>
@@ -2711,7 +2705,7 @@
         <v>35.883629999999997</v>
       </c>
     </row>
-    <row r="87" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B87">
         <v>15</v>
       </c>
@@ -2737,7 +2731,7 @@
         <v>99.925124999999994</v>
       </c>
     </row>
-    <row r="88" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B88">
         <v>15</v>
       </c>
@@ -2763,7 +2757,7 @@
         <v>43.9163</v>
       </c>
     </row>
-    <row r="89" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B89">
         <v>15</v>
       </c>
@@ -2789,7 +2783,7 @@
         <v>48.215865999999998</v>
       </c>
     </row>
-    <row r="90" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B90">
         <v>15</v>
       </c>
@@ -2815,7 +2809,7 @@
         <v>124.18344999999999</v>
       </c>
     </row>
-    <row r="91" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B91">
         <v>15</v>
       </c>
@@ -2841,7 +2835,7 @@
         <v>49.113639999999997</v>
       </c>
     </row>
-    <row r="92" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B92">
         <v>15</v>
       </c>
@@ -2867,7 +2861,7 @@
         <v>66.881399999999999</v>
       </c>
     </row>
-    <row r="93" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="1">
         <v>16</v>
       </c>
@@ -2893,7 +2887,7 @@
         <v>112.68944500000001</v>
       </c>
     </row>
-    <row r="94" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="1">
         <v>16</v>
       </c>
@@ -2919,7 +2913,7 @@
         <v>38.494520000000001</v>
       </c>
     </row>
-    <row r="95" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="1">
         <v>16</v>
       </c>
@@ -2945,7 +2939,7 @@
         <v>36.946303999999998</v>
       </c>
     </row>
-    <row r="96" spans="2:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="1">
         <v>16</v>
       </c>
@@ -2971,7 +2965,7 @@
         <v>68.568550000000002</v>
       </c>
     </row>
-    <row r="97" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="1">
         <v>16</v>
       </c>
@@ -2997,7 +2991,7 @@
         <v>54.046840000000003</v>
       </c>
     </row>
-    <row r="98" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="1">
         <v>16</v>
       </c>
@@ -3023,7 +3017,7 @@
         <v>53.924689999999998</v>
       </c>
     </row>
-    <row r="99" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="1">
         <v>17</v>
       </c>
@@ -3049,7 +3043,7 @@
         <v>56.175243000000002</v>
       </c>
     </row>
-    <row r="100" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="1">
         <v>17</v>
       </c>
@@ -3075,7 +3069,7 @@
         <v>87.840230000000005</v>
       </c>
     </row>
-    <row r="101" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="1">
         <v>17</v>
       </c>
@@ -3101,7 +3095,7 @@
         <v>47.786822999999998</v>
       </c>
     </row>
-    <row r="102" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="1">
         <v>17</v>
       </c>
@@ -3127,7 +3121,7 @@
         <v>98.228806000000006</v>
       </c>
     </row>
-    <row r="103" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="1">
         <v>17</v>
       </c>
@@ -3153,7 +3147,7 @@
         <v>24.220154000000001</v>
       </c>
     </row>
-    <row r="104" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="1">
         <v>17</v>
       </c>
@@ -3179,7 +3173,7 @@
         <v>38.463979999999999</v>
       </c>
     </row>
-    <row r="105" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" s="1">
         <v>18</v>
       </c>
@@ -3201,11 +3195,14 @@
       <c r="H105" s="2">
         <v>2</v>
       </c>
+      <c r="I105">
+        <v>116.62103999999999</v>
+      </c>
       <c r="K105" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="1">
         <v>18</v>
       </c>
@@ -3227,8 +3224,11 @@
       <c r="H106" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="I106">
+        <v>103.62616</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" s="1">
         <v>18</v>
       </c>
@@ -3250,8 +3250,11 @@
       <c r="H107" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="I107">
+        <v>88.547160000000005</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" s="1">
         <v>18</v>
       </c>
@@ -3273,8 +3276,11 @@
       <c r="H108" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="I108">
+        <v>134.0361</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" s="1">
         <v>18</v>
       </c>
@@ -3296,8 +3302,11 @@
       <c r="H109" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="2:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="I109">
+        <v>101.160324</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" s="1">
         <v>18</v>
       </c>
@@ -3318,6 +3327,9 @@
       </c>
       <c r="H110" s="2">
         <v>2</v>
+      </c>
+      <c r="I110">
+        <v>115.44538</v>
       </c>
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -3342,6 +3354,9 @@
       <c r="H111" s="2">
         <v>2</v>
       </c>
+      <c r="I111">
+        <v>118.80898999999999</v>
+      </c>
       <c r="K111" t="s">
         <v>14</v>
       </c>
@@ -3368,8 +3383,11 @@
       <c r="H112" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I112">
+        <v>119.37086499999999</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" s="1">
         <v>19</v>
       </c>
@@ -3391,8 +3409,11 @@
       <c r="H113" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I113">
+        <v>83.191024999999996</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" s="1">
         <v>19</v>
       </c>
@@ -3414,8 +3435,11 @@
       <c r="H114" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I114">
+        <v>126.53628999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" s="1">
         <v>19</v>
       </c>
@@ -3437,8 +3461,11 @@
       <c r="H115" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I115">
+        <v>67.608170000000001</v>
+      </c>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" s="1">
         <v>19</v>
       </c>
@@ -3459,6 +3486,9 @@
       </c>
       <c r="H116" s="2">
         <v>2</v>
+      </c>
+      <c r="I116">
+        <v>119.97702</v>
       </c>
     </row>
   </sheetData>
